--- a/backend/rendimientos.xlsx
+++ b/backend/rendimientos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29803"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\5678v\Desktop\PASANTIA ING CHAIRA\COMPARACION REVISTAS\COMPARACION\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SIB\CIC B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C78CBB6C-05D1-43BF-93B6-E672182F66EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E25A886D-DC15-4451-A21B-DD40DCFF1CA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1572" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2083" uniqueCount="196">
   <si>
     <t>CADECO 2024</t>
   </si>
@@ -600,6 +600,15 @@
   </si>
   <si>
     <t>gl</t>
+  </si>
+  <si>
+    <t>Materiales</t>
+  </si>
+  <si>
+    <t>Mano de Obra</t>
+  </si>
+  <si>
+    <t>Herramiento y Equipo</t>
   </si>
 </sst>
 </file>
@@ -759,14 +768,14 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1086,15 +1095,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D695"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:E695"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.28515625" customWidth="1"/>
-    <col min="2" max="2" width="52.85546875" style="2" customWidth="1"/>
-    <col min="3" max="4" width="12.85546875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="4.33203125" customWidth="1"/>
+    <col min="2" max="2" width="52.88671875" style="2" customWidth="1"/>
+    <col min="3" max="4" width="12.88671875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="17"/>
       <c r="B1" s="18" t="s">
         <v>0</v>
@@ -1106,15 +1115,15 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="17"/>
-      <c r="B2" s="22" t="s">
+      <c r="B2" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1126,7 +1135,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4">
         <f>IF(C5="Rendimiento",A3+1,A3)</f>
         <v>1</v>
@@ -1141,7 +1150,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5">
         <f t="shared" ref="A5:A68" si="0">IF(C6="Rendimiento",A4+1,A4)</f>
         <v>1</v>
@@ -1155,8 +1164,11 @@
       <c r="D5" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E5" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -1170,8 +1182,11 @@
       <c r="D6" s="6" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E6" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -1185,8 +1200,11 @@
       <c r="D7" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E7" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -1200,8 +1218,11 @@
       <c r="D8" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E8" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -1215,8 +1236,11 @@
       <c r="D9" s="6" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E9" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -1230,8 +1254,11 @@
       <c r="D10" s="6" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E10" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -1245,8 +1272,11 @@
       <c r="D11" s="6" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E11" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -1260,8 +1290,11 @@
       <c r="D12" s="6" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E12" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13">
         <f t="shared" si="0"/>
         <v>2</v>
@@ -1274,7 +1307,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14">
         <f t="shared" si="0"/>
         <v>2</v>
@@ -1289,7 +1322,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15">
         <f t="shared" si="0"/>
         <v>2</v>
@@ -1303,8 +1336,11 @@
       <c r="D15" s="6" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E15" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16">
         <f t="shared" si="0"/>
         <v>2</v>
@@ -1318,8 +1354,11 @@
       <c r="D16" s="6" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E16" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17">
         <f t="shared" si="0"/>
         <v>2</v>
@@ -1333,8 +1372,11 @@
       <c r="D17" s="6" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E17" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -1347,7 +1389,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -1362,7 +1404,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -1376,8 +1418,11 @@
       <c r="D20" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E20" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -1391,8 +1436,11 @@
       <c r="D21" s="6" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E21" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -1406,8 +1454,11 @@
       <c r="D22" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E22" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -1421,8 +1472,11 @@
       <c r="D23" s="6" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E23" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -1436,8 +1490,11 @@
       <c r="D24" s="6" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E24" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -1451,8 +1508,11 @@
       <c r="D25" s="6" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E25" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -1465,7 +1525,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -1480,7 +1540,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -1494,8 +1554,11 @@
       <c r="D28" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E28" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -1509,8 +1572,11 @@
       <c r="D29" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E29" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -1524,8 +1590,11 @@
       <c r="D30" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E30" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -1539,8 +1608,11 @@
       <c r="D31" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E31" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -1553,7 +1625,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -1568,7 +1640,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -1582,8 +1654,11 @@
       <c r="D34" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E34" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -1597,8 +1672,11 @@
       <c r="D35" s="6" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E35" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -1612,8 +1690,11 @@
       <c r="D36" s="6" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E36" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -1627,8 +1708,11 @@
       <c r="D37" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E37" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -1642,8 +1726,11 @@
       <c r="D38" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E38" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -1657,8 +1744,11 @@
       <c r="D39" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E39" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -1671,7 +1761,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -1686,7 +1776,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -1700,8 +1790,11 @@
       <c r="D42" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E42" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -1715,8 +1808,11 @@
       <c r="D43" s="6" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E43" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -1730,8 +1826,11 @@
       <c r="D44" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E44" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -1745,8 +1844,11 @@
       <c r="D45" s="6" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E45" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -1760,8 +1862,11 @@
       <c r="D46" s="6" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E46" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -1775,8 +1880,11 @@
       <c r="D47" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E47" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -1790,8 +1898,11 @@
       <c r="D48" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E48" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -1805,8 +1916,11 @@
       <c r="D49" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E49" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -1820,8 +1934,11 @@
       <c r="D50" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E50" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -1834,7 +1951,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -1849,7 +1966,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -1863,8 +1980,11 @@
       <c r="D53" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E53" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -1878,8 +1998,11 @@
       <c r="D54" s="6" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E54" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -1893,8 +2016,11 @@
       <c r="D55" s="6" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E55" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -1908,8 +2034,11 @@
       <c r="D56" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E56" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -1923,8 +2052,11 @@
       <c r="D57" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E57" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -1937,7 +2069,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -1952,7 +2084,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -1966,8 +2098,11 @@
       <c r="D60" s="6" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E60" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -1981,8 +2116,11 @@
       <c r="D61" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E61" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -1996,8 +2134,11 @@
       <c r="D62" s="6" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E62" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -2011,8 +2152,11 @@
       <c r="D63" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E63" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -2026,8 +2170,11 @@
       <c r="D64" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E64" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -2040,7 +2187,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -2055,7 +2202,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A67">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -2069,8 +2216,11 @@
       <c r="D67" s="6" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E67" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -2084,8 +2234,11 @@
       <c r="D68" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E68" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A69">
         <f t="shared" ref="A69:A75" si="1">IF(C70="Rendimiento",A68+1,A68)</f>
         <v>9</v>
@@ -2099,8 +2252,11 @@
       <c r="D69" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E69" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A70">
         <f t="shared" si="1"/>
         <v>10</v>
@@ -2113,7 +2269,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A71">
         <f t="shared" si="1"/>
         <v>10</v>
@@ -2128,7 +2284,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A72">
         <f t="shared" si="1"/>
         <v>10</v>
@@ -2142,8 +2298,11 @@
       <c r="D72" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E72" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73">
         <f t="shared" si="1"/>
         <v>10</v>
@@ -2157,8 +2316,11 @@
       <c r="D73" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E73" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A74">
         <f t="shared" si="1"/>
         <v>10</v>
@@ -2172,8 +2334,11 @@
       <c r="D74" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E74" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A75">
         <f t="shared" si="1"/>
         <v>10</v>
@@ -2187,8 +2352,11 @@
       <c r="D75" s="6" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E75" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76">
         <f t="shared" ref="A76:A139" si="2">IF(C77="Rendimiento",A75+1,A75)</f>
         <v>10</v>
@@ -2202,8 +2370,11 @@
       <c r="D76" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E76" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A77">
         <f t="shared" si="2"/>
         <v>10</v>
@@ -2217,8 +2388,11 @@
       <c r="D77" s="6" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E77" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78">
         <f t="shared" si="2"/>
         <v>10</v>
@@ -2232,8 +2406,11 @@
       <c r="D78" s="6" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E78" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A79">
         <f t="shared" si="2"/>
         <v>10</v>
@@ -2247,8 +2424,11 @@
       <c r="D79" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E79" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A80">
         <f t="shared" si="2"/>
         <v>10</v>
@@ -2262,8 +2442,11 @@
       <c r="D80" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E80" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A81">
         <f t="shared" si="2"/>
         <v>10</v>
@@ -2277,8 +2460,11 @@
       <c r="D81" s="8" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E81" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A82">
         <f t="shared" si="2"/>
         <v>10</v>
@@ -2292,8 +2478,11 @@
       <c r="D82" s="8" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E82" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83">
         <f t="shared" si="2"/>
         <v>11</v>
@@ -2306,7 +2495,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A84">
         <f t="shared" si="2"/>
         <v>11</v>
@@ -2321,7 +2510,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A85">
         <f t="shared" si="2"/>
         <v>11</v>
@@ -2335,8 +2524,11 @@
       <c r="D85" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E85" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86">
         <f t="shared" si="2"/>
         <v>11</v>
@@ -2350,8 +2542,11 @@
       <c r="D86" s="6" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E86" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A87">
         <f t="shared" si="2"/>
         <v>11</v>
@@ -2365,8 +2560,11 @@
       <c r="D87" s="6" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E87" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A88">
         <f t="shared" si="2"/>
         <v>11</v>
@@ -2380,8 +2578,11 @@
       <c r="D88" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E88" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A89">
         <f t="shared" si="2"/>
         <v>11</v>
@@ -2395,8 +2596,11 @@
       <c r="D89" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E89" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A90">
         <f t="shared" si="2"/>
         <v>11</v>
@@ -2410,8 +2614,11 @@
       <c r="D90" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E90" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A91">
         <f t="shared" si="2"/>
         <v>12</v>
@@ -2424,7 +2631,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A92">
         <f t="shared" si="2"/>
         <v>12</v>
@@ -2439,7 +2646,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A93">
         <f t="shared" si="2"/>
         <v>12</v>
@@ -2453,8 +2660,11 @@
       <c r="D93" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E93" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A94">
         <f t="shared" si="2"/>
         <v>12</v>
@@ -2468,8 +2678,11 @@
       <c r="D94" s="6" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E94" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A95">
         <f t="shared" si="2"/>
         <v>12</v>
@@ -2483,8 +2696,11 @@
       <c r="D95" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E95" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A96">
         <f t="shared" si="2"/>
         <v>12</v>
@@ -2498,8 +2714,11 @@
       <c r="D96" s="6" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E96" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A97">
         <f t="shared" si="2"/>
         <v>12</v>
@@ -2513,8 +2732,11 @@
       <c r="D97" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E97" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A98">
         <f t="shared" si="2"/>
         <v>12</v>
@@ -2528,8 +2750,11 @@
       <c r="D98" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E98" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A99">
         <f t="shared" si="2"/>
         <v>13</v>
@@ -2542,7 +2767,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A100">
         <f t="shared" si="2"/>
         <v>13</v>
@@ -2557,7 +2782,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A101">
         <f t="shared" si="2"/>
         <v>13</v>
@@ -2571,8 +2796,11 @@
       <c r="D101" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E101" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A102">
         <f t="shared" si="2"/>
         <v>13</v>
@@ -2586,8 +2814,11 @@
       <c r="D102" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E102" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A103">
         <f t="shared" si="2"/>
         <v>13</v>
@@ -2601,8 +2832,11 @@
       <c r="D103" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E103" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A104">
         <f t="shared" si="2"/>
         <v>14</v>
@@ -2615,7 +2849,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A105">
         <f t="shared" si="2"/>
         <v>14</v>
@@ -2630,7 +2864,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A106">
         <f t="shared" si="2"/>
         <v>14</v>
@@ -2644,8 +2878,11 @@
       <c r="D106" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E106" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A107">
         <f t="shared" si="2"/>
         <v>14</v>
@@ -2659,8 +2896,11 @@
       <c r="D107" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E107" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A108">
         <f t="shared" si="2"/>
         <v>14</v>
@@ -2674,8 +2914,11 @@
       <c r="D108" s="6" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E108" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A109">
         <f t="shared" si="2"/>
         <v>14</v>
@@ -2689,8 +2932,11 @@
       <c r="D109" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E109" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A110">
         <f t="shared" si="2"/>
         <v>14</v>
@@ -2704,8 +2950,11 @@
       <c r="D110" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E110" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A111">
         <f t="shared" si="2"/>
         <v>15</v>
@@ -2718,7 +2967,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A112">
         <f t="shared" si="2"/>
         <v>15</v>
@@ -2733,7 +2982,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A113">
         <f t="shared" si="2"/>
         <v>15</v>
@@ -2747,8 +2996,11 @@
       <c r="D113" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E113" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A114">
         <f t="shared" si="2"/>
         <v>15</v>
@@ -2762,8 +3014,11 @@
       <c r="D114" s="6" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E114" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A115">
         <f t="shared" si="2"/>
         <v>15</v>
@@ -2777,8 +3032,11 @@
       <c r="D115" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E115" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A116">
         <f t="shared" si="2"/>
         <v>15</v>
@@ -2792,8 +3050,11 @@
       <c r="D116" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E116" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A117">
         <f t="shared" si="2"/>
         <v>16</v>
@@ -2806,7 +3067,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A118">
         <f t="shared" si="2"/>
         <v>16</v>
@@ -2821,7 +3082,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A119">
         <f t="shared" si="2"/>
         <v>16</v>
@@ -2835,8 +3096,11 @@
       <c r="D119" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E119" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A120">
         <f t="shared" si="2"/>
         <v>16</v>
@@ -2850,8 +3114,11 @@
       <c r="D120" s="6" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E120" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A121">
         <f t="shared" si="2"/>
         <v>16</v>
@@ -2865,8 +3132,11 @@
       <c r="D121" s="6" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E121" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A122">
         <f t="shared" si="2"/>
         <v>16</v>
@@ -2880,8 +3150,11 @@
       <c r="D122" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E122" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A123">
         <f t="shared" si="2"/>
         <v>16</v>
@@ -2895,8 +3168,11 @@
       <c r="D123" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E123" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A124">
         <f t="shared" si="2"/>
         <v>16</v>
@@ -2910,8 +3186,11 @@
       <c r="D124" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E124" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A125">
         <f t="shared" si="2"/>
         <v>17</v>
@@ -2924,7 +3203,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A126">
         <f t="shared" si="2"/>
         <v>17</v>
@@ -2939,7 +3218,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A127">
         <f t="shared" si="2"/>
         <v>17</v>
@@ -2953,8 +3232,11 @@
       <c r="D127" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E127" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A128">
         <f t="shared" si="2"/>
         <v>17</v>
@@ -2968,8 +3250,11 @@
       <c r="D128" s="6" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E128" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A129">
         <f t="shared" si="2"/>
         <v>17</v>
@@ -2983,8 +3268,11 @@
       <c r="D129" s="6" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E129" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A130">
         <f t="shared" si="2"/>
         <v>17</v>
@@ -2998,8 +3286,11 @@
       <c r="D130" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E130" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A131">
         <f t="shared" si="2"/>
         <v>17</v>
@@ -3013,8 +3304,11 @@
       <c r="D131" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E131" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A132">
         <f t="shared" si="2"/>
         <v>18</v>
@@ -3027,7 +3321,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A133">
         <f t="shared" si="2"/>
         <v>18</v>
@@ -3042,7 +3336,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A134">
         <f t="shared" si="2"/>
         <v>18</v>
@@ -3056,8 +3350,11 @@
       <c r="D134" s="6" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E134" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A135">
         <f t="shared" si="2"/>
         <v>18</v>
@@ -3071,8 +3368,11 @@
       <c r="D135" s="6" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E135" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A136">
         <f t="shared" si="2"/>
         <v>18</v>
@@ -3086,8 +3386,11 @@
       <c r="D136" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E136" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A137">
         <f t="shared" si="2"/>
         <v>18</v>
@@ -3101,8 +3404,11 @@
       <c r="D137" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E137" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A138">
         <f t="shared" si="2"/>
         <v>19</v>
@@ -3115,7 +3421,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A139">
         <f t="shared" si="2"/>
         <v>19</v>
@@ -3130,7 +3436,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A140">
         <f t="shared" ref="A140:A142" si="3">IF(C141="Rendimiento",A139+1,A139)</f>
         <v>19</v>
@@ -3144,8 +3450,11 @@
       <c r="D140" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E140" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A141">
         <f t="shared" si="3"/>
         <v>19</v>
@@ -3159,8 +3468,11 @@
       <c r="D141" s="6" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E141" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A142">
         <f t="shared" si="3"/>
         <v>19</v>
@@ -3174,8 +3486,11 @@
       <c r="D142" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E142" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A143">
         <f t="shared" ref="A143:A192" si="4">IF(C144="Rendimiento",A142+1,A142)</f>
         <v>19</v>
@@ -3189,8 +3504,11 @@
       <c r="D143" s="6" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E143" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A144">
         <f t="shared" si="4"/>
         <v>19</v>
@@ -3204,8 +3522,11 @@
       <c r="D144" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E144" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A145">
         <f t="shared" si="4"/>
         <v>19</v>
@@ -3219,8 +3540,11 @@
       <c r="D145" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E145" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A146">
         <f t="shared" si="4"/>
         <v>19</v>
@@ -3234,8 +3558,11 @@
       <c r="D146" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E146" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A147">
         <f t="shared" si="4"/>
         <v>20</v>
@@ -3248,7 +3575,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A148">
         <f t="shared" si="4"/>
         <v>20</v>
@@ -3263,7 +3590,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A149">
         <f t="shared" si="4"/>
         <v>20</v>
@@ -3277,8 +3604,11 @@
       <c r="D149" s="6" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E149" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A150">
         <f t="shared" si="4"/>
         <v>20</v>
@@ -3292,8 +3622,11 @@
       <c r="D150" s="6" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E150" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A151">
         <f t="shared" si="4"/>
         <v>20</v>
@@ -3307,8 +3640,11 @@
       <c r="D151" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E151" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A152">
         <f t="shared" si="4"/>
         <v>20</v>
@@ -3322,8 +3658,11 @@
       <c r="D152" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E152" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A153">
         <f t="shared" si="4"/>
         <v>21</v>
@@ -3336,7 +3675,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A154">
         <f t="shared" si="4"/>
         <v>21</v>
@@ -3351,7 +3690,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A155">
         <f t="shared" si="4"/>
         <v>21</v>
@@ -3365,8 +3704,11 @@
       <c r="D155" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E155" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A156">
         <f t="shared" si="4"/>
         <v>21</v>
@@ -3380,8 +3722,11 @@
       <c r="D156" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E156" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A157">
         <f t="shared" si="4"/>
         <v>21</v>
@@ -3395,8 +3740,11 @@
       <c r="D157" s="6" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E157" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A158">
         <f t="shared" si="4"/>
         <v>21</v>
@@ -3410,8 +3758,11 @@
       <c r="D158" s="6" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E158" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A159">
         <f t="shared" si="4"/>
         <v>21</v>
@@ -3425,8 +3776,11 @@
       <c r="D159" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E159" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A160">
         <f t="shared" si="4"/>
         <v>21</v>
@@ -3440,8 +3794,11 @@
       <c r="D160" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E160" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A161">
         <f t="shared" si="4"/>
         <v>22</v>
@@ -3454,7 +3811,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A162">
         <f t="shared" si="4"/>
         <v>22</v>
@@ -3469,7 +3826,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="163" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A163">
         <f t="shared" si="4"/>
         <v>22</v>
@@ -3483,8 +3840,11 @@
       <c r="D163" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="164" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E163" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A164">
         <f t="shared" si="4"/>
         <v>22</v>
@@ -3498,8 +3858,11 @@
       <c r="D164" s="6" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E164" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A165">
         <f t="shared" si="4"/>
         <v>22</v>
@@ -3513,8 +3876,11 @@
       <c r="D165" s="6" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E165" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A166">
         <f t="shared" si="4"/>
         <v>22</v>
@@ -3528,8 +3894,11 @@
       <c r="D166" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="167" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E166" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A167">
         <f t="shared" si="4"/>
         <v>22</v>
@@ -3543,8 +3912,11 @@
       <c r="D167" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="168" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E167" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A168">
         <f t="shared" si="4"/>
         <v>23</v>
@@ -3557,7 +3929,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="169" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A169">
         <f t="shared" si="4"/>
         <v>23</v>
@@ -3572,7 +3944,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="170" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A170">
         <f t="shared" si="4"/>
         <v>23</v>
@@ -3586,8 +3958,11 @@
       <c r="D170" s="6" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="171" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E170" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A171">
         <f t="shared" si="4"/>
         <v>24</v>
@@ -3600,7 +3975,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="172" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A172">
         <f t="shared" si="4"/>
         <v>24</v>
@@ -3615,7 +3990,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="173" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A173">
         <f t="shared" si="4"/>
         <v>24</v>
@@ -3629,8 +4004,11 @@
       <c r="D173" s="6" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="174" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E173" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A174">
         <f t="shared" si="4"/>
         <v>25</v>
@@ -3643,7 +4021,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="175" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A175">
         <f t="shared" si="4"/>
         <v>25</v>
@@ -3658,7 +4036,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="176" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A176">
         <f t="shared" si="4"/>
         <v>25</v>
@@ -3672,8 +4050,11 @@
       <c r="D176" s="6" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E176" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A177">
         <f t="shared" si="4"/>
         <v>26</v>
@@ -3686,7 +4067,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="178" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A178">
         <f t="shared" si="4"/>
         <v>26</v>
@@ -3701,7 +4082,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="179" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A179">
         <f t="shared" si="4"/>
         <v>26</v>
@@ -3715,8 +4096,11 @@
       <c r="D179" s="6" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E179" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A180">
         <f t="shared" si="4"/>
         <v>27</v>
@@ -3729,7 +4113,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="181" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A181">
         <f t="shared" si="4"/>
         <v>27</v>
@@ -3744,7 +4128,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="182" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A182">
         <f t="shared" si="4"/>
         <v>27</v>
@@ -3758,8 +4142,11 @@
       <c r="D182" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="183" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E182" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A183">
         <f t="shared" si="4"/>
         <v>27</v>
@@ -3773,8 +4160,11 @@
       <c r="D183" s="6" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="184" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E183" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A184">
         <f t="shared" si="4"/>
         <v>27</v>
@@ -3788,8 +4178,11 @@
       <c r="D184" s="6" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="185" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E184" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A185">
         <f t="shared" si="4"/>
         <v>27</v>
@@ -3803,8 +4196,11 @@
       <c r="D185" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="186" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E185" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="186" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A186">
         <f t="shared" si="4"/>
         <v>27</v>
@@ -3818,8 +4214,11 @@
       <c r="D186" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="187" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E186" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A187">
         <f t="shared" si="4"/>
         <v>28</v>
@@ -3832,7 +4231,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="188" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A188">
         <f t="shared" si="4"/>
         <v>28</v>
@@ -3847,7 +4246,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="189" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A189">
         <f t="shared" si="4"/>
         <v>28</v>
@@ -3861,8 +4260,11 @@
       <c r="D189" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="190" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E189" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A190">
         <f t="shared" si="4"/>
         <v>28</v>
@@ -3876,8 +4278,11 @@
       <c r="D190" s="6" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="191" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E190" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="191" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A191">
         <f t="shared" si="4"/>
         <v>28</v>
@@ -3891,8 +4296,11 @@
       <c r="D191" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="192" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E191" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="192" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A192">
         <f t="shared" si="4"/>
         <v>28</v>
@@ -3906,8 +4314,11 @@
       <c r="D192" s="6" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="193" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E192" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="193" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A193">
         <f t="shared" ref="A193:A218" si="5">IF(C194="Rendimiento",A192+1,A192)</f>
         <v>28</v>
@@ -3921,8 +4332,11 @@
       <c r="D193" s="6" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="194" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E193" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="194" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A194">
         <f t="shared" si="5"/>
         <v>28</v>
@@ -3936,8 +4350,11 @@
       <c r="D194" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="195" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E194" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="195" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A195">
         <f t="shared" si="5"/>
         <v>28</v>
@@ -3951,8 +4368,11 @@
       <c r="D195" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="196" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E195" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="196" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A196">
         <f t="shared" si="5"/>
         <v>28</v>
@@ -3966,8 +4386,11 @@
       <c r="D196" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="197" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E196" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A197">
         <f t="shared" si="5"/>
         <v>28</v>
@@ -3981,8 +4404,11 @@
       <c r="D197" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="198" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E197" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A198">
         <f t="shared" si="5"/>
         <v>28</v>
@@ -3996,8 +4422,11 @@
       <c r="D198" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="199" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E198" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A199">
         <f t="shared" si="5"/>
         <v>28</v>
@@ -4011,8 +4440,11 @@
       <c r="D199" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="200" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E199" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="200" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A200">
         <f t="shared" si="5"/>
         <v>29</v>
@@ -4025,7 +4457,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="201" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A201">
         <f t="shared" si="5"/>
         <v>29</v>
@@ -4040,7 +4472,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="202" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A202">
         <f t="shared" si="5"/>
         <v>29</v>
@@ -4054,8 +4486,11 @@
       <c r="D202" s="6" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="203" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E202" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="203" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A203">
         <f t="shared" si="5"/>
         <v>29</v>
@@ -4069,8 +4504,11 @@
       <c r="D203" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="204" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E203" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="204" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A204">
         <f t="shared" si="5"/>
         <v>29</v>
@@ -4084,8 +4522,11 @@
       <c r="D204" s="6" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="205" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E204" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="205" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A205">
         <f t="shared" si="5"/>
         <v>29</v>
@@ -4099,8 +4540,11 @@
       <c r="D205" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="206" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E205" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="206" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A206">
         <f t="shared" si="5"/>
         <v>29</v>
@@ -4114,8 +4558,11 @@
       <c r="D206" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="207" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E206" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="207" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A207">
         <f t="shared" si="5"/>
         <v>30</v>
@@ -4128,7 +4575,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="208" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A208">
         <f t="shared" si="5"/>
         <v>30</v>
@@ -4143,7 +4590,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="209" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A209">
         <f t="shared" si="5"/>
         <v>30</v>
@@ -4157,8 +4604,11 @@
       <c r="D209" s="6" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="210" spans="1:4" ht="24" x14ac:dyDescent="0.25">
+      <c r="E209" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="210" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A210">
         <f t="shared" si="5"/>
         <v>31</v>
@@ -4171,7 +4621,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="211" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A211">
         <f t="shared" si="5"/>
         <v>31</v>
@@ -4186,7 +4636,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="212" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A212">
         <f t="shared" si="5"/>
         <v>31</v>
@@ -4200,8 +4650,11 @@
       <c r="D212" s="6" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="213" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E212" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="213" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A213">
         <f t="shared" si="5"/>
         <v>31</v>
@@ -4215,8 +4668,11 @@
       <c r="D213" s="6" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="214" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E213" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="214" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A214">
         <f t="shared" si="5"/>
         <v>31</v>
@@ -4230,8 +4686,11 @@
       <c r="D214" s="6" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="215" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E214" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="215" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A215">
         <f t="shared" si="5"/>
         <v>32</v>
@@ -4244,7 +4703,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="216" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A216">
         <f t="shared" si="5"/>
         <v>32</v>
@@ -4259,7 +4718,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="217" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A217">
         <f t="shared" si="5"/>
         <v>32</v>
@@ -4273,8 +4732,11 @@
       <c r="D217" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="218" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E217" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="218" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A218">
         <f t="shared" si="5"/>
         <v>32</v>
@@ -4288,8 +4750,11 @@
       <c r="D218" s="6" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="219" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E218" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="219" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A219">
         <f t="shared" ref="A219:A282" si="6">IF(C220="Rendimiento",A218+1,A218)</f>
         <v>32</v>
@@ -4303,8 +4768,11 @@
       <c r="D219" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="220" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E219" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="220" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A220">
         <f t="shared" si="6"/>
         <v>32</v>
@@ -4318,8 +4786,11 @@
       <c r="D220" s="6" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="221" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E220" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="221" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A221">
         <f t="shared" si="6"/>
         <v>32</v>
@@ -4333,8 +4804,11 @@
       <c r="D221" s="6" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="222" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E221" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="222" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A222">
         <f t="shared" si="6"/>
         <v>32</v>
@@ -4348,8 +4822,11 @@
       <c r="D222" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="223" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E222" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="223" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A223">
         <f t="shared" si="6"/>
         <v>32</v>
@@ -4363,8 +4840,11 @@
       <c r="D223" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="224" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E223" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="224" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A224">
         <f t="shared" si="6"/>
         <v>32</v>
@@ -4378,8 +4858,11 @@
       <c r="D224" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="225" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E224" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="225" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A225">
         <f t="shared" si="6"/>
         <v>32</v>
@@ -4393,8 +4876,11 @@
       <c r="D225" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="226" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E225" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="226" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A226">
         <f t="shared" si="6"/>
         <v>32</v>
@@ -4408,8 +4894,11 @@
       <c r="D226" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="227" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E226" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="227" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A227">
         <f t="shared" si="6"/>
         <v>33</v>
@@ -4422,7 +4911,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="228" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A228">
         <f t="shared" si="6"/>
         <v>33</v>
@@ -4437,7 +4926,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="229" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A229">
         <f t="shared" si="6"/>
         <v>33</v>
@@ -4451,8 +4940,11 @@
       <c r="D229" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="230" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E229" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="230" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A230">
         <f t="shared" si="6"/>
         <v>33</v>
@@ -4466,8 +4958,11 @@
       <c r="D230" s="6" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="231" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E230" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="231" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A231">
         <f t="shared" si="6"/>
         <v>33</v>
@@ -4481,8 +4976,11 @@
       <c r="D231" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="232" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E231" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="232" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A232">
         <f t="shared" si="6"/>
         <v>33</v>
@@ -4496,8 +4994,11 @@
       <c r="D232" s="6" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="233" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E232" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="233" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A233">
         <f t="shared" si="6"/>
         <v>33</v>
@@ -4511,8 +5012,11 @@
       <c r="D233" s="6" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="234" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E233" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="234" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A234">
         <f t="shared" si="6"/>
         <v>33</v>
@@ -4526,8 +5030,11 @@
       <c r="D234" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="235" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E234" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="235" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A235">
         <f t="shared" si="6"/>
         <v>33</v>
@@ -4541,8 +5048,11 @@
       <c r="D235" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="236" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E235" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="236" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A236">
         <f t="shared" si="6"/>
         <v>33</v>
@@ -4556,8 +5066,11 @@
       <c r="D236" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="237" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E236" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="237" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A237">
         <f t="shared" si="6"/>
         <v>33</v>
@@ -4571,8 +5084,11 @@
       <c r="D237" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="238" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E237" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="238" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A238">
         <f t="shared" si="6"/>
         <v>33</v>
@@ -4586,8 +5102,11 @@
       <c r="D238" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="239" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E238" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="239" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A239">
         <f t="shared" si="6"/>
         <v>34</v>
@@ -4600,7 +5119,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="240" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A240">
         <f t="shared" si="6"/>
         <v>34</v>
@@ -4615,7 +5134,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="241" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A241">
         <f t="shared" si="6"/>
         <v>34</v>
@@ -4629,8 +5148,11 @@
       <c r="D241" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="242" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E241" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="242" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A242">
         <f t="shared" si="6"/>
         <v>34</v>
@@ -4644,8 +5166,11 @@
       <c r="D242" s="6" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="243" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E242" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="243" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A243">
         <f t="shared" si="6"/>
         <v>34</v>
@@ -4659,8 +5184,11 @@
       <c r="D243" s="6" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="244" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E243" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="244" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A244">
         <f t="shared" si="6"/>
         <v>34</v>
@@ -4674,8 +5202,11 @@
       <c r="D244" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="245" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E244" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="245" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A245">
         <f t="shared" si="6"/>
         <v>34</v>
@@ -4689,8 +5220,11 @@
       <c r="D245" s="6" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="246" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E245" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="246" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A246">
         <f t="shared" si="6"/>
         <v>34</v>
@@ -4704,8 +5238,11 @@
       <c r="D246" s="6" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="247" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E246" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="247" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A247">
         <f t="shared" si="6"/>
         <v>34</v>
@@ -4719,8 +5256,11 @@
       <c r="D247" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="248" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E247" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="248" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A248">
         <f t="shared" si="6"/>
         <v>34</v>
@@ -4734,8 +5274,11 @@
       <c r="D248" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="249" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E248" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="249" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A249">
         <f t="shared" si="6"/>
         <v>34</v>
@@ -4749,8 +5292,11 @@
       <c r="D249" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="250" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E249" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="250" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A250">
         <f t="shared" si="6"/>
         <v>34</v>
@@ -4764,8 +5310,11 @@
       <c r="D250" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="251" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E250" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="251" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A251">
         <f t="shared" si="6"/>
         <v>35</v>
@@ -4778,7 +5327,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="252" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A252">
         <f t="shared" si="6"/>
         <v>35</v>
@@ -4793,7 +5342,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="253" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A253">
         <f t="shared" si="6"/>
         <v>35</v>
@@ -4807,8 +5356,11 @@
       <c r="D253" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="254" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E253" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="254" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A254">
         <f t="shared" si="6"/>
         <v>35</v>
@@ -4822,8 +5374,11 @@
       <c r="D254" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="255" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E254" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="255" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A255">
         <f t="shared" si="6"/>
         <v>35</v>
@@ -4837,8 +5392,11 @@
       <c r="D255" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="256" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E255" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="256" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A256">
         <f t="shared" si="6"/>
         <v>36</v>
@@ -4851,7 +5409,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="257" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A257">
         <f t="shared" si="6"/>
         <v>36</v>
@@ -4866,7 +5424,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="258" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A258">
         <f t="shared" si="6"/>
         <v>36</v>
@@ -4880,8 +5438,11 @@
       <c r="D258" s="6" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="259" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E258" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="259" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A259">
         <f t="shared" si="6"/>
         <v>36</v>
@@ -4895,8 +5456,11 @@
       <c r="D259" s="6" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="260" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E259" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="260" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A260">
         <f t="shared" si="6"/>
         <v>36</v>
@@ -4910,8 +5474,11 @@
       <c r="D260" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="261" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E260" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="261" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A261">
         <f t="shared" si="6"/>
         <v>36</v>
@@ -4925,8 +5492,11 @@
       <c r="D261" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="262" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E261" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="262" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A262">
         <f t="shared" si="6"/>
         <v>37</v>
@@ -4939,7 +5509,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="263" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A263">
         <f t="shared" si="6"/>
         <v>37</v>
@@ -4954,7 +5524,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="264" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A264">
         <f t="shared" si="6"/>
         <v>37</v>
@@ -4968,8 +5538,11 @@
       <c r="D264" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="265" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E264" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="265" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A265">
         <f t="shared" si="6"/>
         <v>37</v>
@@ -4983,8 +5556,11 @@
       <c r="D265" s="6" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="266" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E265" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="266" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A266">
         <f t="shared" si="6"/>
         <v>37</v>
@@ -4998,8 +5574,11 @@
       <c r="D266" s="10" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="267" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E266" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="267" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A267">
         <f t="shared" si="6"/>
         <v>37</v>
@@ -5013,8 +5592,11 @@
       <c r="D267" s="10" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="268" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E267" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="268" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A268">
         <f t="shared" si="6"/>
         <v>38</v>
@@ -5027,7 +5609,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="269" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A269">
         <f t="shared" si="6"/>
         <v>38</v>
@@ -5042,7 +5624,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="270" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A270">
         <f t="shared" si="6"/>
         <v>38</v>
@@ -5056,8 +5638,11 @@
       <c r="D270" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="271" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E270" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="271" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A271">
         <f t="shared" si="6"/>
         <v>38</v>
@@ -5071,8 +5656,11 @@
       <c r="D271" s="6" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="272" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E271" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="272" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A272">
         <f t="shared" si="6"/>
         <v>38</v>
@@ -5086,8 +5674,11 @@
       <c r="D272" s="6" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="273" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E272" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="273" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A273">
         <f t="shared" si="6"/>
         <v>38</v>
@@ -5101,8 +5692,11 @@
       <c r="D273" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="274" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E273" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="274" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A274">
         <f t="shared" si="6"/>
         <v>38</v>
@@ -5116,8 +5710,11 @@
       <c r="D274" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="275" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E274" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="275" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A275">
         <f t="shared" si="6"/>
         <v>39</v>
@@ -5130,7 +5727,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="276" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A276">
         <f t="shared" si="6"/>
         <v>39</v>
@@ -5145,7 +5742,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="277" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A277">
         <f t="shared" si="6"/>
         <v>39</v>
@@ -5159,8 +5756,11 @@
       <c r="D277" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="278" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E277" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="278" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A278">
         <f t="shared" si="6"/>
         <v>39</v>
@@ -5174,8 +5774,11 @@
       <c r="D278" s="6" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="279" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E278" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="279" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A279">
         <f t="shared" si="6"/>
         <v>39</v>
@@ -5189,8 +5792,11 @@
       <c r="D279" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="280" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E279" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="280" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A280">
         <f t="shared" si="6"/>
         <v>39</v>
@@ -5204,8 +5810,11 @@
       <c r="D280" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="281" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E280" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="281" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A281">
         <f t="shared" si="6"/>
         <v>40</v>
@@ -5218,7 +5827,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="282" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A282">
         <f t="shared" si="6"/>
         <v>40</v>
@@ -5233,7 +5842,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="283" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A283">
         <f t="shared" ref="A283:A293" si="7">IF(C284="Rendimiento",A282+1,A282)</f>
         <v>40</v>
@@ -5247,8 +5856,11 @@
       <c r="D283" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="284" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E283" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="284" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A284">
         <f t="shared" si="7"/>
         <v>40</v>
@@ -5262,8 +5874,11 @@
       <c r="D284" s="6" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="285" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E284" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="285" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A285">
         <f t="shared" si="7"/>
         <v>40</v>
@@ -5277,8 +5892,11 @@
       <c r="D285" s="6" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="286" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E285" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="286" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A286">
         <f t="shared" si="7"/>
         <v>40</v>
@@ -5292,8 +5910,11 @@
       <c r="D286" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="287" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E286" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="287" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A287">
         <f t="shared" si="7"/>
         <v>40</v>
@@ -5307,8 +5928,11 @@
       <c r="D287" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="288" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E287" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="288" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A288">
         <f t="shared" si="7"/>
         <v>41</v>
@@ -5321,7 +5945,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="289" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A289">
         <f t="shared" si="7"/>
         <v>41</v>
@@ -5336,7 +5960,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="290" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A290">
         <f t="shared" si="7"/>
         <v>41</v>
@@ -5350,8 +5974,11 @@
       <c r="D290" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="291" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E290" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="291" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A291">
         <f t="shared" si="7"/>
         <v>41</v>
@@ -5365,8 +5992,11 @@
       <c r="D291" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="292" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E291" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="292" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A292">
         <f t="shared" si="7"/>
         <v>41</v>
@@ -5380,8 +6010,11 @@
       <c r="D292" s="6" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="293" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E292" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="293" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A293">
         <f t="shared" si="7"/>
         <v>41</v>
@@ -5395,8 +6028,11 @@
       <c r="D293" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="294" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E293" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="294" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A294">
         <f t="shared" ref="A294:A354" si="8">IF(C295="Rendimiento",A293+1,A293)</f>
         <v>41</v>
@@ -5410,8 +6046,11 @@
       <c r="D294" s="6" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="295" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E294" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="295" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A295">
         <f t="shared" si="8"/>
         <v>41</v>
@@ -5425,8 +6064,11 @@
       <c r="D295" s="6" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="296" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E295" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="296" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A296">
         <f t="shared" si="8"/>
         <v>41</v>
@@ -5440,8 +6082,11 @@
       <c r="D296" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="297" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E296" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="297" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A297">
         <f t="shared" si="8"/>
         <v>41</v>
@@ -5455,8 +6100,11 @@
       <c r="D297" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="298" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E297" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="298" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A298">
         <f t="shared" si="8"/>
         <v>41</v>
@@ -5470,8 +6118,11 @@
       <c r="D298" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="299" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E298" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="299" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A299">
         <f t="shared" si="8"/>
         <v>41</v>
@@ -5485,8 +6136,11 @@
       <c r="D299" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="300" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E299" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="300" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A300">
         <f t="shared" si="8"/>
         <v>41</v>
@@ -5500,8 +6154,11 @@
       <c r="D300" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="301" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E300" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="301" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A301">
         <f t="shared" si="8"/>
         <v>42</v>
@@ -5514,7 +6171,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="302" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A302">
         <f t="shared" si="8"/>
         <v>42</v>
@@ -5529,7 +6186,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="303" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A303">
         <f t="shared" si="8"/>
         <v>42</v>
@@ -5543,8 +6200,11 @@
       <c r="D303" s="6" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="304" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E303" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="304" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A304">
         <f t="shared" si="8"/>
         <v>42</v>
@@ -5558,8 +6218,11 @@
       <c r="D304" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="305" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E304" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="305" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A305">
         <f t="shared" si="8"/>
         <v>42</v>
@@ -5573,8 +6236,11 @@
       <c r="D305" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="306" spans="1:4" ht="24" x14ac:dyDescent="0.25">
+      <c r="E305" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="306" spans="1:5" ht="24" x14ac:dyDescent="0.3">
       <c r="A306">
         <f t="shared" si="8"/>
         <v>43</v>
@@ -5587,7 +6253,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="307" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A307">
         <f t="shared" si="8"/>
         <v>43</v>
@@ -5602,7 +6268,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="308" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A308">
         <f t="shared" si="8"/>
         <v>43</v>
@@ -5616,8 +6282,11 @@
       <c r="D308" s="6" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="309" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E308" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="309" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A309">
         <f t="shared" si="8"/>
         <v>43</v>
@@ -5631,8 +6300,11 @@
       <c r="D309" s="6" t="s">
         <v>191</v>
       </c>
-    </row>
-    <row r="310" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E309" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="310" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A310">
         <f t="shared" si="8"/>
         <v>43</v>
@@ -5646,8 +6318,11 @@
       <c r="D310" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="311" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E310" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="311" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A311">
         <f t="shared" si="8"/>
         <v>43</v>
@@ -5661,8 +6336,11 @@
       <c r="D311" s="10" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="312" spans="1:4" ht="24" x14ac:dyDescent="0.25">
+      <c r="E311" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="312" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A312">
         <f t="shared" si="8"/>
         <v>44</v>
@@ -5675,7 +6353,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="313" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A313">
         <f t="shared" si="8"/>
         <v>44</v>
@@ -5690,7 +6368,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="314" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A314">
         <f t="shared" si="8"/>
         <v>44</v>
@@ -5704,8 +6382,11 @@
       <c r="D314" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="315" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E314" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="315" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A315">
         <f t="shared" si="8"/>
         <v>44</v>
@@ -5719,8 +6400,11 @@
       <c r="D315" s="6" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="316" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E315" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="316" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A316">
         <f t="shared" si="8"/>
         <v>44</v>
@@ -5734,8 +6418,11 @@
       <c r="D316" s="6" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="317" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E316" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="317" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A317">
         <f t="shared" si="8"/>
         <v>44</v>
@@ -5749,8 +6436,11 @@
       <c r="D317" s="6" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="318" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E317" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="318" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A318">
         <f t="shared" si="8"/>
         <v>44</v>
@@ -5764,8 +6454,11 @@
       <c r="D318" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="319" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E318" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="319" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A319">
         <f t="shared" si="8"/>
         <v>44</v>
@@ -5779,8 +6472,11 @@
       <c r="D319" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="320" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E319" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="320" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A320">
         <f t="shared" si="8"/>
         <v>44</v>
@@ -5794,8 +6490,11 @@
       <c r="D320" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="321" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E320" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="321" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A321">
         <f t="shared" si="8"/>
         <v>45</v>
@@ -5808,7 +6507,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="322" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A322">
         <f t="shared" si="8"/>
         <v>45</v>
@@ -5823,7 +6522,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="323" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A323">
         <f t="shared" si="8"/>
         <v>45</v>
@@ -5837,8 +6536,11 @@
       <c r="D323" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="324" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E323" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="324" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A324">
         <f t="shared" si="8"/>
         <v>45</v>
@@ -5852,8 +6554,11 @@
       <c r="D324" s="6" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="325" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E324" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="325" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A325">
         <f t="shared" si="8"/>
         <v>45</v>
@@ -5867,8 +6572,11 @@
       <c r="D325" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="326" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E325" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="326" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A326">
         <f t="shared" si="8"/>
         <v>45</v>
@@ -5882,8 +6590,11 @@
       <c r="D326" s="6" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="327" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E326" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="327" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A327">
         <f t="shared" si="8"/>
         <v>45</v>
@@ -5897,8 +6608,11 @@
       <c r="D327" s="10" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="328" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E327" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="328" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A328">
         <f t="shared" si="8"/>
         <v>45</v>
@@ -5912,8 +6626,11 @@
       <c r="D328" s="10" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="329" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E328" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="329" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A329">
         <f t="shared" si="8"/>
         <v>46</v>
@@ -5926,7 +6643,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="330" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A330">
         <f t="shared" si="8"/>
         <v>46</v>
@@ -5941,7 +6658,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="331" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A331">
         <f t="shared" si="8"/>
         <v>46</v>
@@ -5955,8 +6672,11 @@
       <c r="D331" s="6" t="s">
         <v>191</v>
       </c>
-    </row>
-    <row r="332" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E331" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="332" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A332">
         <f t="shared" si="8"/>
         <v>46</v>
@@ -5970,8 +6690,11 @@
       <c r="D332" s="6" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="333" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E332" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="333" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A333">
         <f t="shared" si="8"/>
         <v>46</v>
@@ -5985,8 +6708,11 @@
       <c r="D333" s="10" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="334" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E333" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="334" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A334">
         <f t="shared" si="8"/>
         <v>46</v>
@@ -6000,8 +6726,11 @@
       <c r="D334" s="12" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="335" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E334" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="335" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A335">
         <f t="shared" si="8"/>
         <v>47</v>
@@ -6014,7 +6743,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="336" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A336">
         <f t="shared" si="8"/>
         <v>47</v>
@@ -6029,7 +6758,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="337" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A337">
         <f t="shared" si="8"/>
         <v>47</v>
@@ -6043,8 +6772,11 @@
       <c r="D337" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="338" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E337" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="338" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A338">
         <f t="shared" si="8"/>
         <v>47</v>
@@ -6058,8 +6790,11 @@
       <c r="D338" s="10" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="339" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E338" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="339" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A339">
         <f t="shared" si="8"/>
         <v>47</v>
@@ -6073,8 +6808,11 @@
       <c r="D339" s="12" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="340" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E339" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="340" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A340">
         <f t="shared" si="8"/>
         <v>47</v>
@@ -6088,8 +6826,11 @@
       <c r="D340" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="341" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E340" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="341" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A341">
         <f t="shared" si="8"/>
         <v>47</v>
@@ -6103,8 +6844,11 @@
       <c r="D341" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="342" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E341" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="342" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A342">
         <f t="shared" si="8"/>
         <v>48</v>
@@ -6117,7 +6861,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="343" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A343">
         <f t="shared" si="8"/>
         <v>48</v>
@@ -6132,7 +6876,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="344" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A344">
         <f t="shared" si="8"/>
         <v>48</v>
@@ -6146,8 +6890,11 @@
       <c r="D344" s="6" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="345" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E344" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="345" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A345">
         <f t="shared" si="8"/>
         <v>49</v>
@@ -6160,7 +6907,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="346" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A346">
         <f t="shared" si="8"/>
         <v>49</v>
@@ -6175,7 +6922,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="347" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A347">
         <f t="shared" si="8"/>
         <v>49</v>
@@ -6189,8 +6936,11 @@
       <c r="D347" s="14" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="348" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E347" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="348" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A348">
         <f t="shared" si="8"/>
         <v>49</v>
@@ -6204,8 +6954,11 @@
       <c r="D348" s="14" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="349" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E348" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="349" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A349">
         <f t="shared" si="8"/>
         <v>49</v>
@@ -6219,8 +6972,11 @@
       <c r="D349" s="14" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="350" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E349" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="350" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A350">
         <f t="shared" si="8"/>
         <v>49</v>
@@ -6234,8 +6990,11 @@
       <c r="D350" s="14" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="351" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E350" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="351" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A351">
         <f t="shared" si="8"/>
         <v>49</v>
@@ -6249,8 +7008,11 @@
       <c r="D351" s="14" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="352" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E351" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="352" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A352">
         <f t="shared" si="8"/>
         <v>50</v>
@@ -6263,7 +7025,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="353" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A353">
         <f t="shared" si="8"/>
         <v>50</v>
@@ -6278,7 +7040,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="354" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A354">
         <f t="shared" si="8"/>
         <v>50</v>
@@ -6292,8 +7054,11 @@
       <c r="D354" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="355" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E354" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="355" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A355">
         <f t="shared" ref="A355:A380" si="9">IF(C356="Rendimiento",A354+1,A354)</f>
         <v>50</v>
@@ -6307,8 +7072,11 @@
       <c r="D355" s="6" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="356" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E355" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="356" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A356">
         <f t="shared" si="9"/>
         <v>50</v>
@@ -6322,8 +7090,11 @@
       <c r="D356" s="6" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="357" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E356" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="357" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A357">
         <f t="shared" si="9"/>
         <v>50</v>
@@ -6337,8 +7108,11 @@
       <c r="D357" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="358" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E357" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="358" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A358">
         <f t="shared" si="9"/>
         <v>50</v>
@@ -6352,8 +7126,11 @@
       <c r="D358" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="359" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E358" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="359" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A359">
         <f t="shared" si="9"/>
         <v>51</v>
@@ -6366,7 +7143,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="360" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A360">
         <f t="shared" si="9"/>
         <v>51</v>
@@ -6381,7 +7158,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="361" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A361">
         <f t="shared" si="9"/>
         <v>51</v>
@@ -6395,8 +7172,11 @@
       <c r="D361" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="362" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E361" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="362" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A362">
         <f t="shared" si="9"/>
         <v>51</v>
@@ -6410,8 +7190,11 @@
       <c r="D362" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="363" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E362" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="363" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A363">
         <f t="shared" si="9"/>
         <v>51</v>
@@ -6425,8 +7208,11 @@
       <c r="D363" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="364" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E363" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="364" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A364">
         <f t="shared" si="9"/>
         <v>51</v>
@@ -6440,8 +7226,11 @@
       <c r="D364" s="6" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="365" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E364" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="365" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A365">
         <f t="shared" si="9"/>
         <v>51</v>
@@ -6455,8 +7244,11 @@
       <c r="D365" s="6" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="366" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E365" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="366" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A366">
         <f t="shared" si="9"/>
         <v>51</v>
@@ -6470,8 +7262,11 @@
       <c r="D366" s="6" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="367" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E366" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="367" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A367">
         <f t="shared" si="9"/>
         <v>51</v>
@@ -6485,8 +7280,11 @@
       <c r="D367" s="6" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="368" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E367" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="368" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A368">
         <f t="shared" si="9"/>
         <v>51</v>
@@ -6500,8 +7298,11 @@
       <c r="D368" s="6" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="369" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E368" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="369" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A369">
         <f t="shared" si="9"/>
         <v>52</v>
@@ -6514,7 +7315,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="370" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A370">
         <f t="shared" si="9"/>
         <v>52</v>
@@ -6529,7 +7330,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="371" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A371">
         <f t="shared" si="9"/>
         <v>52</v>
@@ -6543,8 +7344,11 @@
       <c r="D371" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="372" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E371" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="372" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A372">
         <f t="shared" si="9"/>
         <v>52</v>
@@ -6558,8 +7362,11 @@
       <c r="D372" s="6" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="373" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E372" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="373" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A373">
         <f t="shared" si="9"/>
         <v>52</v>
@@ -6573,8 +7380,11 @@
       <c r="D373" s="6" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="374" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E373" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="374" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A374">
         <f t="shared" si="9"/>
         <v>52</v>
@@ -6588,8 +7398,11 @@
       <c r="D374" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="375" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E374" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="375" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A375">
         <f t="shared" si="9"/>
         <v>52</v>
@@ -6603,8 +7416,11 @@
       <c r="D375" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="376" spans="1:4" ht="24" x14ac:dyDescent="0.25">
+      <c r="E375" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="376" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A376">
         <f t="shared" si="9"/>
         <v>53</v>
@@ -6617,7 +7433,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="377" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A377">
         <f t="shared" si="9"/>
         <v>53</v>
@@ -6632,7 +7448,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="378" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A378">
         <f t="shared" si="9"/>
         <v>53</v>
@@ -6646,8 +7462,11 @@
       <c r="D378" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="379" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E378" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="379" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A379">
         <f t="shared" si="9"/>
         <v>53</v>
@@ -6661,8 +7480,11 @@
       <c r="D379" s="6" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="380" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E379" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="380" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A380">
         <f t="shared" si="9"/>
         <v>53</v>
@@ -6676,8 +7498,11 @@
       <c r="D380" s="6" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="381" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E380" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="381" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A381">
         <f t="shared" ref="A381:A436" si="10">IF(C382="Rendimiento",A380+1,A380)</f>
         <v>53</v>
@@ -6691,8 +7516,11 @@
       <c r="D381" s="6" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="382" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E381" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="382" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A382">
         <f t="shared" si="10"/>
         <v>53</v>
@@ -6706,8 +7534,11 @@
       <c r="D382" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="383" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E382" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="383" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A383">
         <f t="shared" si="10"/>
         <v>53</v>
@@ -6721,8 +7552,11 @@
       <c r="D383" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="384" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E383" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="384" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A384">
         <f t="shared" si="10"/>
         <v>53</v>
@@ -6736,8 +7570,11 @@
       <c r="D384" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="385" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E384" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="385" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A385">
         <f t="shared" si="10"/>
         <v>54</v>
@@ -6750,7 +7587,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="386" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A386">
         <f t="shared" si="10"/>
         <v>54</v>
@@ -6765,7 +7602,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="387" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A387">
         <f t="shared" si="10"/>
         <v>54</v>
@@ -6779,8 +7616,11 @@
       <c r="D387" s="14" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="388" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E387" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="388" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A388">
         <f t="shared" si="10"/>
         <v>54</v>
@@ -6794,8 +7634,11 @@
       <c r="D388" s="14" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="389" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E388" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="389" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A389">
         <f t="shared" si="10"/>
         <v>54</v>
@@ -6809,8 +7652,11 @@
       <c r="D389" s="14" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="390" spans="1:4" ht="24" x14ac:dyDescent="0.25">
+      <c r="E389" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="390" spans="1:5" ht="24" x14ac:dyDescent="0.3">
       <c r="A390">
         <f t="shared" si="10"/>
         <v>55</v>
@@ -6823,7 +7669,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="391" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A391">
         <f t="shared" si="10"/>
         <v>55</v>
@@ -6838,7 +7684,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="392" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A392">
         <f t="shared" si="10"/>
         <v>55</v>
@@ -6852,8 +7698,11 @@
       <c r="D392" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="393" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E392" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="393" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A393">
         <f t="shared" si="10"/>
         <v>55</v>
@@ -6867,8 +7716,11 @@
       <c r="D393" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="394" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E393" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="394" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A394">
         <f t="shared" si="10"/>
         <v>55</v>
@@ -6882,8 +7734,11 @@
       <c r="D394" s="6" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="395" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E394" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="395" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A395">
         <f t="shared" si="10"/>
         <v>55</v>
@@ -6897,8 +7752,11 @@
       <c r="D395" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="396" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E395" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="396" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A396">
         <f t="shared" si="10"/>
         <v>55</v>
@@ -6912,8 +7770,11 @@
       <c r="D396" s="6" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="397" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E396" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="397" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A397">
         <f t="shared" si="10"/>
         <v>55</v>
@@ -6927,8 +7788,11 @@
       <c r="D397" s="6" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="398" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E397" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="398" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A398">
         <f t="shared" si="10"/>
         <v>55</v>
@@ -6942,8 +7806,11 @@
       <c r="D398" s="6" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="399" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E398" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="399" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A399">
         <f t="shared" si="10"/>
         <v>55</v>
@@ -6957,8 +7824,11 @@
       <c r="D399" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="400" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E399" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="400" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A400">
         <f t="shared" si="10"/>
         <v>55</v>
@@ -6972,8 +7842,11 @@
       <c r="D400" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="401" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E400" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="401" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A401">
         <f t="shared" si="10"/>
         <v>55</v>
@@ -6987,8 +7860,11 @@
       <c r="D401" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="402" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E401" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="402" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A402">
         <f t="shared" si="10"/>
         <v>56</v>
@@ -7001,7 +7877,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="403" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A403">
         <f t="shared" si="10"/>
         <v>56</v>
@@ -7016,7 +7892,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="404" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A404">
         <f t="shared" si="10"/>
         <v>56</v>
@@ -7030,8 +7906,11 @@
       <c r="D404" s="6" t="s">
         <v>191</v>
       </c>
-    </row>
-    <row r="405" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E404" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="405" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A405">
         <f t="shared" si="10"/>
         <v>56</v>
@@ -7045,8 +7924,11 @@
       <c r="D405" s="6" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="406" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E405" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="406" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A406">
         <f t="shared" si="10"/>
         <v>56</v>
@@ -7060,8 +7942,11 @@
       <c r="D406" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="407" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E406" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="407" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A407">
         <f t="shared" si="10"/>
         <v>56</v>
@@ -7075,8 +7960,11 @@
       <c r="D407" s="8" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="408" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E407" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="408" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A408">
         <f t="shared" si="10"/>
         <v>57</v>
@@ -7089,7 +7977,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="409" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A409">
         <f t="shared" si="10"/>
         <v>57</v>
@@ -7104,7 +7992,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="410" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A410">
         <f t="shared" si="10"/>
         <v>57</v>
@@ -7118,8 +8006,11 @@
       <c r="D410" s="6" t="s">
         <v>192</v>
       </c>
-    </row>
-    <row r="411" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E410" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="411" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A411">
         <f t="shared" si="10"/>
         <v>57</v>
@@ -7133,8 +8024,11 @@
       <c r="D411" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="412" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E411" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="412" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A412">
         <f t="shared" si="10"/>
         <v>57</v>
@@ -7148,8 +8042,11 @@
       <c r="D412" s="8" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="413" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E412" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="413" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A413">
         <f t="shared" si="10"/>
         <v>57</v>
@@ -7163,8 +8060,11 @@
       <c r="D413" s="6" t="s">
         <v>192</v>
       </c>
-    </row>
-    <row r="414" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E413" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="414" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A414">
         <f t="shared" si="10"/>
         <v>57</v>
@@ -7178,8 +8078,11 @@
       <c r="D414" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="415" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E414" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="415" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A415">
         <f t="shared" si="10"/>
         <v>57</v>
@@ -7193,8 +8096,11 @@
       <c r="D415" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="416" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E415" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="416" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A416">
         <f t="shared" si="10"/>
         <v>58</v>
@@ -7207,7 +8113,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="417" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A417">
         <f t="shared" si="10"/>
         <v>58</v>
@@ -7222,7 +8128,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="418" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A418">
         <f t="shared" si="10"/>
         <v>58</v>
@@ -7236,8 +8142,11 @@
       <c r="D418" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="419" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E418" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="419" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A419">
         <f t="shared" si="10"/>
         <v>58</v>
@@ -7251,8 +8160,11 @@
       <c r="D419" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="420" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E419" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="420" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A420">
         <f t="shared" si="10"/>
         <v>58</v>
@@ -7266,8 +8178,11 @@
       <c r="D420" s="6" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="421" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E420" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="421" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A421">
         <f t="shared" si="10"/>
         <v>58</v>
@@ -7281,8 +8196,11 @@
       <c r="D421" s="6" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="422" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E421" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="422" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A422">
         <f t="shared" si="10"/>
         <v>58</v>
@@ -7296,8 +8214,11 @@
       <c r="D422" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="423" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E422" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="423" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A423">
         <f t="shared" si="10"/>
         <v>58</v>
@@ -7311,8 +8232,11 @@
       <c r="D423" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="424" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E423" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="424" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A424">
         <f t="shared" si="10"/>
         <v>58</v>
@@ -7326,8 +8250,11 @@
       <c r="D424" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="425" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E424" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="425" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A425">
         <f t="shared" si="10"/>
         <v>59</v>
@@ -7340,7 +8267,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="426" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A426">
         <f t="shared" si="10"/>
         <v>59</v>
@@ -7355,7 +8282,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="427" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A427">
         <f t="shared" si="10"/>
         <v>59</v>
@@ -7369,8 +8296,11 @@
       <c r="D427" s="6" t="s">
         <v>192</v>
       </c>
-    </row>
-    <row r="428" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E427" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="428" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A428">
         <f t="shared" si="10"/>
         <v>59</v>
@@ -7384,8 +8314,11 @@
       <c r="D428" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="429" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E428" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="429" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A429">
         <f t="shared" si="10"/>
         <v>59</v>
@@ -7399,8 +8332,11 @@
       <c r="D429" s="8" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="430" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E429" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="430" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A430">
         <f t="shared" si="10"/>
         <v>59</v>
@@ -7414,8 +8350,11 @@
       <c r="D430" s="6" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="431" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E430" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="431" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A431">
         <f t="shared" si="10"/>
         <v>59</v>
@@ -7429,8 +8368,11 @@
       <c r="D431" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="432" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E431" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="432" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A432">
         <f t="shared" si="10"/>
         <v>59</v>
@@ -7444,8 +8386,11 @@
       <c r="D432" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="433" spans="1:4" ht="24" x14ac:dyDescent="0.25">
+      <c r="E432" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="433" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A433">
         <f t="shared" si="10"/>
         <v>60</v>
@@ -7458,7 +8403,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="434" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A434">
         <f t="shared" si="10"/>
         <v>60</v>
@@ -7473,7 +8418,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="435" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A435">
         <f t="shared" si="10"/>
         <v>60</v>
@@ -7487,8 +8432,11 @@
       <c r="D435" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="436" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E435" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="436" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A436">
         <f t="shared" si="10"/>
         <v>60</v>
@@ -7502,8 +8450,11 @@
       <c r="D436" s="6" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="437" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E436" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="437" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A437">
         <f t="shared" ref="A437:A500" si="11">IF(C438="Rendimiento",A436+1,A436)</f>
         <v>60</v>
@@ -7517,8 +8468,11 @@
       <c r="D437" s="6" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="438" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E437" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="438" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A438">
         <f t="shared" si="11"/>
         <v>60</v>
@@ -7532,8 +8486,11 @@
       <c r="D438" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="439" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E438" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="439" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A439">
         <f t="shared" si="11"/>
         <v>60</v>
@@ -7547,8 +8504,11 @@
       <c r="D439" s="6" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="440" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E439" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="440" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A440">
         <f t="shared" si="11"/>
         <v>60</v>
@@ -7562,8 +8522,11 @@
       <c r="D440" s="6" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="441" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E440" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="441" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A441">
         <f t="shared" si="11"/>
         <v>60</v>
@@ -7577,8 +8540,11 @@
       <c r="D441" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="442" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E441" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="442" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A442">
         <f t="shared" si="11"/>
         <v>60</v>
@@ -7592,8 +8558,11 @@
       <c r="D442" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="443" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E442" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="443" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A443">
         <f t="shared" si="11"/>
         <v>60</v>
@@ -7607,8 +8576,11 @@
       <c r="D443" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="444" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E443" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="444" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A444">
         <f t="shared" si="11"/>
         <v>61</v>
@@ -7621,7 +8593,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="445" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A445">
         <f t="shared" si="11"/>
         <v>61</v>
@@ -7636,7 +8608,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="446" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A446">
         <f t="shared" si="11"/>
         <v>61</v>
@@ -7650,8 +8622,11 @@
       <c r="D446" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="447" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E446" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="447" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A447">
         <f t="shared" si="11"/>
         <v>61</v>
@@ -7665,8 +8640,11 @@
       <c r="D447" s="6" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="448" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E447" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="448" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A448">
         <f t="shared" si="11"/>
         <v>61</v>
@@ -7680,8 +8658,11 @@
       <c r="D448" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="449" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E448" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="449" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A449">
         <f t="shared" si="11"/>
         <v>61</v>
@@ -7695,8 +8676,11 @@
       <c r="D449" s="6" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="450" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E449" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="450" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A450">
         <f t="shared" si="11"/>
         <v>61</v>
@@ -7710,8 +8694,11 @@
       <c r="D450" s="6" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="451" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E450" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="451" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A451">
         <f t="shared" si="11"/>
         <v>61</v>
@@ -7725,8 +8712,11 @@
       <c r="D451" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="452" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E451" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="452" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A452">
         <f t="shared" si="11"/>
         <v>61</v>
@@ -7740,8 +8730,11 @@
       <c r="D452" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="453" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E452" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="453" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A453">
         <f t="shared" si="11"/>
         <v>61</v>
@@ -7755,8 +8748,11 @@
       <c r="D453" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="454" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E453" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="454" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A454">
         <f t="shared" si="11"/>
         <v>61</v>
@@ -7770,8 +8766,11 @@
       <c r="D454" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="455" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E454" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="455" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A455">
         <f t="shared" si="11"/>
         <v>61</v>
@@ -7785,8 +8784,11 @@
       <c r="D455" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="456" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E455" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="456" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A456">
         <f t="shared" si="11"/>
         <v>62</v>
@@ -7799,7 +8801,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="457" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A457">
         <f t="shared" si="11"/>
         <v>62</v>
@@ -7814,7 +8816,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="458" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A458">
         <f t="shared" si="11"/>
         <v>62</v>
@@ -7828,8 +8830,11 @@
       <c r="D458" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="459" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E458" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="459" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A459">
         <f t="shared" si="11"/>
         <v>62</v>
@@ -7843,8 +8848,11 @@
       <c r="D459" s="6" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="460" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E459" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="460" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A460">
         <f t="shared" si="11"/>
         <v>62</v>
@@ -7858,8 +8866,11 @@
       <c r="D460" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="461" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E460" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="461" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A461">
         <f t="shared" si="11"/>
         <v>62</v>
@@ -7873,8 +8884,11 @@
       <c r="D461" s="6" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="462" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E461" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="462" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A462">
         <f t="shared" si="11"/>
         <v>62</v>
@@ -7888,8 +8902,11 @@
       <c r="D462" s="6" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="463" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E462" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="463" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A463">
         <f t="shared" si="11"/>
         <v>62</v>
@@ -7903,8 +8920,11 @@
       <c r="D463" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="464" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E463" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="464" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A464">
         <f t="shared" si="11"/>
         <v>62</v>
@@ -7918,8 +8938,11 @@
       <c r="D464" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="465" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E464" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="465" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A465">
         <f t="shared" si="11"/>
         <v>62</v>
@@ -7933,8 +8956,11 @@
       <c r="D465" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="466" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E465" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="466" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A466">
         <f t="shared" si="11"/>
         <v>62</v>
@@ -7948,8 +8974,11 @@
       <c r="D466" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="467" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E466" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="467" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A467">
         <f t="shared" si="11"/>
         <v>62</v>
@@ -7963,8 +8992,11 @@
       <c r="D467" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="468" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E467" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="468" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A468">
         <f t="shared" si="11"/>
         <v>63</v>
@@ -7977,7 +9009,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="469" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A469">
         <f t="shared" si="11"/>
         <v>63</v>
@@ -7992,7 +9024,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="470" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A470">
         <f t="shared" si="11"/>
         <v>63</v>
@@ -8006,8 +9038,11 @@
       <c r="D470" s="6" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="471" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E470" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="471" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A471">
         <f t="shared" si="11"/>
         <v>63</v>
@@ -8021,8 +9056,11 @@
       <c r="D471" s="6" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="472" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E471" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="472" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A472">
         <f t="shared" si="11"/>
         <v>63</v>
@@ -8036,8 +9074,11 @@
       <c r="D472" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="473" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E472" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="473" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A473">
         <f t="shared" si="11"/>
         <v>63</v>
@@ -8051,8 +9092,11 @@
       <c r="D473" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="474" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E473" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="474" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A474">
         <f t="shared" si="11"/>
         <v>63</v>
@@ -8066,8 +9110,11 @@
       <c r="D474" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="475" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E474" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="475" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A475">
         <f t="shared" si="11"/>
         <v>64</v>
@@ -8080,7 +9127,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="476" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A476">
         <f t="shared" si="11"/>
         <v>64</v>
@@ -8095,7 +9142,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="477" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A477">
         <f t="shared" si="11"/>
         <v>64</v>
@@ -8109,8 +9156,11 @@
       <c r="D477" s="6" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="478" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E477" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="478" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A478">
         <f t="shared" si="11"/>
         <v>64</v>
@@ -8124,8 +9174,11 @@
       <c r="D478" s="6" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="479" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E478" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="479" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A479">
         <f t="shared" si="11"/>
         <v>64</v>
@@ -8139,8 +9192,11 @@
       <c r="D479" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="480" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E479" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="480" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A480">
         <f t="shared" si="11"/>
         <v>64</v>
@@ -8154,8 +9210,11 @@
       <c r="D480" s="6" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="481" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E480" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="481" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A481">
         <f t="shared" si="11"/>
         <v>64</v>
@@ -8169,8 +9228,11 @@
       <c r="D481" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="482" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E481" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="482" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A482">
         <f t="shared" si="11"/>
         <v>64</v>
@@ -8184,8 +9246,11 @@
       <c r="D482" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="483" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E482" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="483" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A483">
         <f t="shared" si="11"/>
         <v>65</v>
@@ -8198,7 +9263,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="484" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A484">
         <f t="shared" si="11"/>
         <v>65</v>
@@ -8213,7 +9278,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="485" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A485">
         <f t="shared" si="11"/>
         <v>65</v>
@@ -8227,8 +9292,11 @@
       <c r="D485" s="6" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="486" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E485" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="486" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A486">
         <f t="shared" si="11"/>
         <v>66</v>
@@ -8241,7 +9309,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="487" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A487">
         <f t="shared" si="11"/>
         <v>66</v>
@@ -8256,7 +9324,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="488" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A488">
         <f t="shared" si="11"/>
         <v>66</v>
@@ -8270,8 +9338,11 @@
       <c r="D488" s="6" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="489" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E488" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="489" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A489">
         <f t="shared" si="11"/>
         <v>67</v>
@@ -8284,7 +9355,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="490" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A490">
         <f t="shared" si="11"/>
         <v>67</v>
@@ -8299,7 +9370,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="491" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A491">
         <f t="shared" si="11"/>
         <v>67</v>
@@ -8313,8 +9384,11 @@
       <c r="D491" s="6" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="492" spans="1:4" ht="24" x14ac:dyDescent="0.25">
+      <c r="E491" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="492" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A492">
         <f t="shared" si="11"/>
         <v>68</v>
@@ -8327,7 +9401,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="493" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A493">
         <f t="shared" si="11"/>
         <v>68</v>
@@ -8342,7 +9416,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="494" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A494">
         <f t="shared" si="11"/>
         <v>68</v>
@@ -8356,8 +9430,11 @@
       <c r="D494" s="6" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="495" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E494" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="495" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A495">
         <f t="shared" si="11"/>
         <v>69</v>
@@ -8370,7 +9447,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="496" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A496">
         <f t="shared" si="11"/>
         <v>69</v>
@@ -8385,7 +9462,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="497" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A497">
         <f t="shared" si="11"/>
         <v>69</v>
@@ -8399,8 +9476,11 @@
       <c r="D497" s="6" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="498" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E497" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="498" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A498">
         <f t="shared" si="11"/>
         <v>69</v>
@@ -8414,8 +9494,11 @@
       <c r="D498" s="6" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="499" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E498" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="499" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A499">
         <f t="shared" si="11"/>
         <v>69</v>
@@ -8429,8 +9512,11 @@
       <c r="D499" s="6" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="500" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E499" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="500" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A500">
         <f t="shared" si="11"/>
         <v>70</v>
@@ -8443,7 +9529,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="501" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A501">
         <f t="shared" ref="A501:A504" si="12">IF(C502="Rendimiento",A500+1,A500)</f>
         <v>70</v>
@@ -8458,7 +9544,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="502" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A502">
         <f t="shared" si="12"/>
         <v>70</v>
@@ -8472,8 +9558,11 @@
       <c r="D502" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="503" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E502" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="503" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A503">
         <f t="shared" si="12"/>
         <v>70</v>
@@ -8487,8 +9576,11 @@
       <c r="D503" s="6" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="504" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E503" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="504" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A504">
         <f t="shared" si="12"/>
         <v>70</v>
@@ -8502,8 +9594,11 @@
       <c r="D504" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="505" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E504" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="505" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A505">
         <f t="shared" ref="A505:A566" si="13">IF(C506="Rendimiento",A504+1,A504)</f>
         <v>70</v>
@@ -8517,8 +9612,11 @@
       <c r="D505" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="506" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E505" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="506" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A506">
         <f t="shared" si="13"/>
         <v>70</v>
@@ -8532,8 +9630,11 @@
       <c r="D506" s="6" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="507" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E506" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="507" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A507">
         <f t="shared" si="13"/>
         <v>70</v>
@@ -8547,8 +9648,11 @@
       <c r="D507" s="6" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="508" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E507" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="508" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A508">
         <f t="shared" si="13"/>
         <v>70</v>
@@ -8562,8 +9666,11 @@
       <c r="D508" s="6" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="509" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E508" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="509" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A509">
         <f t="shared" si="13"/>
         <v>70</v>
@@ -8577,8 +9684,11 @@
       <c r="D509" s="6" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="510" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E509" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="510" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A510">
         <f t="shared" si="13"/>
         <v>71</v>
@@ -8591,7 +9701,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="511" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A511">
         <f t="shared" si="13"/>
         <v>71</v>
@@ -8606,7 +9716,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="512" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A512">
         <f t="shared" si="13"/>
         <v>71</v>
@@ -8620,8 +9730,11 @@
       <c r="D512" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="513" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E512" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="513" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A513">
         <f t="shared" si="13"/>
         <v>71</v>
@@ -8635,8 +9748,11 @@
       <c r="D513" s="6" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="514" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E513" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="514" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A514">
         <f t="shared" si="13"/>
         <v>71</v>
@@ -8650,8 +9766,11 @@
       <c r="D514" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="515" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E514" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="515" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A515">
         <f t="shared" si="13"/>
         <v>71</v>
@@ -8665,8 +9784,11 @@
       <c r="D515" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="516" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E515" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="516" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A516">
         <f t="shared" si="13"/>
         <v>71</v>
@@ -8680,8 +9802,11 @@
       <c r="D516" s="6" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="517" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E516" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="517" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A517">
         <f t="shared" si="13"/>
         <v>71</v>
@@ -8695,8 +9820,11 @@
       <c r="D517" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="518" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E517" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="518" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A518">
         <f t="shared" si="13"/>
         <v>71</v>
@@ -8710,8 +9838,11 @@
       <c r="D518" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="519" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E518" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="519" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A519">
         <f t="shared" si="13"/>
         <v>72</v>
@@ -8724,7 +9855,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="520" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A520">
         <f t="shared" si="13"/>
         <v>72</v>
@@ -8739,7 +9870,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="521" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A521">
         <f t="shared" si="13"/>
         <v>72</v>
@@ -8753,8 +9884,11 @@
       <c r="D521" s="14" t="s">
         <v>192</v>
       </c>
-    </row>
-    <row r="522" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E521" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="522" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A522">
         <f t="shared" si="13"/>
         <v>72</v>
@@ -8768,8 +9902,11 @@
       <c r="D522" s="14" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="523" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E522" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="523" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A523">
         <f t="shared" si="13"/>
         <v>72</v>
@@ -8783,8 +9920,11 @@
       <c r="D523" s="14" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="524" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E523" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="524" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A524">
         <f t="shared" si="13"/>
         <v>72</v>
@@ -8798,8 +9938,11 @@
       <c r="D524" s="14" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="525" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E524" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="525" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A525">
         <f t="shared" si="13"/>
         <v>72</v>
@@ -8813,8 +9956,11 @@
       <c r="D525" s="14" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="526" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E525" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="526" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A526">
         <f t="shared" si="13"/>
         <v>73</v>
@@ -8827,7 +9973,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="527" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A527">
         <f t="shared" si="13"/>
         <v>73</v>
@@ -8842,7 +9988,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="528" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A528">
         <f t="shared" si="13"/>
         <v>73</v>
@@ -8856,8 +10002,11 @@
       <c r="D528" s="14" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="529" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E528" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="529" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A529">
         <f t="shared" si="13"/>
         <v>73</v>
@@ -8871,8 +10020,11 @@
       <c r="D529" s="14" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="530" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E529" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="530" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A530">
         <f t="shared" si="13"/>
         <v>73</v>
@@ -8886,8 +10038,11 @@
       <c r="D530" s="14" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="531" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E530" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="531" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A531">
         <f t="shared" si="13"/>
         <v>73</v>
@@ -8901,8 +10056,11 @@
       <c r="D531" s="14" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="532" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E531" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="532" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A532">
         <f t="shared" si="13"/>
         <v>73</v>
@@ -8916,8 +10074,11 @@
       <c r="D532" s="14" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="533" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E532" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="533" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A533">
         <f t="shared" si="13"/>
         <v>73</v>
@@ -8931,8 +10092,11 @@
       <c r="D533" s="14" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="534" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E533" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="534" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A534">
         <f t="shared" si="13"/>
         <v>73</v>
@@ -8946,8 +10110,11 @@
       <c r="D534" s="14" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="535" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E534" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="535" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A535">
         <f t="shared" si="13"/>
         <v>73</v>
@@ -8961,8 +10128,11 @@
       <c r="D535" s="14" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="536" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E535" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="536" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A536">
         <f t="shared" si="13"/>
         <v>74</v>
@@ -8975,7 +10145,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="537" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A537">
         <f t="shared" si="13"/>
         <v>74</v>
@@ -8990,7 +10160,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="538" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A538">
         <f t="shared" si="13"/>
         <v>74</v>
@@ -9004,8 +10174,11 @@
       <c r="D538" s="14" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="539" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E538" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="539" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A539">
         <f t="shared" si="13"/>
         <v>74</v>
@@ -9019,8 +10192,11 @@
       <c r="D539" s="14" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="540" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E539" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="540" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A540">
         <f t="shared" si="13"/>
         <v>74</v>
@@ -9034,8 +10210,11 @@
       <c r="D540" s="14" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="541" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E540" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="541" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A541">
         <f t="shared" si="13"/>
         <v>74</v>
@@ -9049,8 +10228,11 @@
       <c r="D541" s="14" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="542" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E541" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="542" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A542">
         <f t="shared" si="13"/>
         <v>74</v>
@@ -9064,8 +10246,11 @@
       <c r="D542" s="14" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="543" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E542" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="543" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A543">
         <f t="shared" si="13"/>
         <v>74</v>
@@ -9079,8 +10264,11 @@
       <c r="D543" s="14" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="544" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E543" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="544" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A544">
         <f t="shared" si="13"/>
         <v>75</v>
@@ -9093,7 +10281,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="545" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A545">
         <f t="shared" si="13"/>
         <v>75</v>
@@ -9108,7 +10296,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="546" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A546">
         <f t="shared" si="13"/>
         <v>75</v>
@@ -9122,8 +10310,11 @@
       <c r="D546" s="14" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="547" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E546" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="547" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A547">
         <f t="shared" si="13"/>
         <v>75</v>
@@ -9137,8 +10328,11 @@
       <c r="D547" s="14" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="548" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E547" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="548" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A548">
         <f t="shared" si="13"/>
         <v>75</v>
@@ -9152,8 +10346,11 @@
       <c r="D548" s="14" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="549" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E548" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="549" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A549">
         <f t="shared" si="13"/>
         <v>75</v>
@@ -9167,8 +10364,11 @@
       <c r="D549" s="14" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="550" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E549" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="550" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A550">
         <f t="shared" si="13"/>
         <v>75</v>
@@ -9182,8 +10382,11 @@
       <c r="D550" s="14" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="551" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E550" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="551" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A551">
         <f t="shared" si="13"/>
         <v>75</v>
@@ -9197,8 +10400,11 @@
       <c r="D551" s="14" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="552" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E551" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="552" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A552">
         <f t="shared" si="13"/>
         <v>76</v>
@@ -9211,7 +10417,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="553" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A553">
         <f t="shared" si="13"/>
         <v>76</v>
@@ -9226,97 +10432,115 @@
         <v>5</v>
       </c>
     </row>
-    <row r="554" spans="1:4" s="23" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A554" s="23">
+    <row r="554" spans="1:5" s="22" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A554" s="22">
         <f t="shared" si="13"/>
         <v>76</v>
       </c>
-      <c r="B554" s="24" t="s">
+      <c r="B554" s="23" t="s">
         <v>56</v>
       </c>
-      <c r="C554" s="25">
+      <c r="C554" s="24">
         <v>13</v>
       </c>
-      <c r="D554" s="25" t="s">
+      <c r="D554" s="24" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="555" spans="1:4" s="23" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A555" s="23">
+      <c r="E554" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="555" spans="1:5" s="22" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A555" s="22">
         <f t="shared" si="13"/>
         <v>76</v>
       </c>
-      <c r="B555" s="24" t="s">
+      <c r="B555" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="C555" s="25">
+      <c r="C555" s="24">
         <v>0.6</v>
       </c>
-      <c r="D555" s="25" t="s">
+      <c r="D555" s="24" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="556" spans="1:4" s="23" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A556" s="23">
+      <c r="E555" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="556" spans="1:5" s="22" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A556" s="22">
         <f t="shared" si="13"/>
         <v>76</v>
       </c>
-      <c r="B556" s="24" t="s">
+      <c r="B556" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="C556" s="25">
+      <c r="C556" s="24">
         <v>0.2</v>
       </c>
-      <c r="D556" s="25" t="s">
+      <c r="D556" s="24" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="557" spans="1:4" s="23" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A557" s="23">
+      <c r="E556" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="557" spans="1:5" s="22" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A557" s="22">
         <f t="shared" si="13"/>
         <v>76</v>
       </c>
-      <c r="B557" s="24" t="s">
+      <c r="B557" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="C557" s="25">
+      <c r="C557" s="24">
         <v>3.9</v>
       </c>
-      <c r="D557" s="25" t="s">
+      <c r="D557" s="24" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="558" spans="1:4" s="23" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A558" s="23">
+      <c r="E557" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="558" spans="1:5" s="22" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A558" s="22">
         <f t="shared" si="13"/>
         <v>76</v>
       </c>
-      <c r="B558" s="24" t="s">
+      <c r="B558" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="C558" s="25">
+      <c r="C558" s="24">
         <v>0.53</v>
       </c>
-      <c r="D558" s="25" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="559" spans="1:4" s="23" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A559" s="23">
+      <c r="D558" s="24" t="s">
+        <v>189</v>
+      </c>
+      <c r="E558" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="559" spans="1:5" s="22" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A559" s="22">
         <f t="shared" si="13"/>
         <v>76</v>
       </c>
-      <c r="B559" s="24" t="s">
+      <c r="B559" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="C559" s="25">
+      <c r="C559" s="24">
         <v>0.53</v>
       </c>
-      <c r="D559" s="25" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="560" spans="1:4" ht="24" x14ac:dyDescent="0.25">
+      <c r="D559" s="24" t="s">
+        <v>189</v>
+      </c>
+      <c r="E559" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="560" spans="1:5" ht="24" x14ac:dyDescent="0.3">
       <c r="A560">
         <f t="shared" si="13"/>
         <v>77</v>
@@ -9329,7 +10553,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="561" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A561">
         <f t="shared" si="13"/>
         <v>77</v>
@@ -9344,7 +10568,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="562" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A562">
         <f t="shared" si="13"/>
         <v>77</v>
@@ -9358,8 +10582,11 @@
       <c r="D562" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="563" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E562" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="563" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A563">
         <f t="shared" si="13"/>
         <v>77</v>
@@ -9373,8 +10600,11 @@
       <c r="D563" s="6" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="564" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E563" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="564" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A564">
         <f t="shared" si="13"/>
         <v>77</v>
@@ -9388,8 +10618,11 @@
       <c r="D564" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="565" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E564" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="565" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A565">
         <f t="shared" si="13"/>
         <v>77</v>
@@ -9403,8 +10636,11 @@
       <c r="D565" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="566" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E565" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="566" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A566">
         <f t="shared" si="13"/>
         <v>77</v>
@@ -9418,8 +10654,11 @@
       <c r="D566" s="6" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="567" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E566" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="567" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A567">
         <f t="shared" ref="A567:A597" si="14">IF(C568="Rendimiento",A566+1,A566)</f>
         <v>77</v>
@@ -9433,8 +10672,11 @@
       <c r="D567" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="568" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E567" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="568" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A568">
         <f t="shared" si="14"/>
         <v>77</v>
@@ -9448,8 +10690,11 @@
       <c r="D568" s="6" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="569" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E568" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="569" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A569">
         <f t="shared" si="14"/>
         <v>77</v>
@@ -9463,8 +10708,11 @@
       <c r="D569" s="6" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="570" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E569" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="570" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A570">
         <f t="shared" si="14"/>
         <v>77</v>
@@ -9478,8 +10726,11 @@
       <c r="D570" s="6" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="571" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E570" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="571" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A571">
         <f t="shared" si="14"/>
         <v>77</v>
@@ -9493,8 +10744,11 @@
       <c r="D571" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="572" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E571" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="572" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A572">
         <f t="shared" si="14"/>
         <v>77</v>
@@ -9508,8 +10762,11 @@
       <c r="D572" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="573" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E572" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="573" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A573">
         <f t="shared" si="14"/>
         <v>77</v>
@@ -9523,8 +10780,11 @@
       <c r="D573" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="574" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E573" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="574" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A574">
         <f t="shared" si="14"/>
         <v>77</v>
@@ -9538,8 +10798,11 @@
       <c r="D574" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="575" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E574" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="575" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A575">
         <f t="shared" si="14"/>
         <v>77</v>
@@ -9553,8 +10816,11 @@
       <c r="D575" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="576" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E575" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="576" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A576">
         <f t="shared" si="14"/>
         <v>77</v>
@@ -9568,8 +10834,11 @@
       <c r="D576" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="577" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E576" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="577" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A577">
         <f t="shared" si="14"/>
         <v>77</v>
@@ -9583,8 +10852,11 @@
       <c r="D577" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="578" spans="1:4" ht="24" x14ac:dyDescent="0.25">
+      <c r="E577" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="578" spans="1:5" ht="24" x14ac:dyDescent="0.3">
       <c r="A578">
         <f t="shared" si="14"/>
         <v>78</v>
@@ -9597,7 +10869,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="579" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A579">
         <f t="shared" si="14"/>
         <v>78</v>
@@ -9612,7 +10884,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="580" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A580">
         <f t="shared" si="14"/>
         <v>78</v>
@@ -9626,8 +10898,11 @@
       <c r="D580" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="581" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E580" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="581" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A581">
         <f t="shared" si="14"/>
         <v>78</v>
@@ -9641,8 +10916,11 @@
       <c r="D581" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="582" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E581" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="582" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A582">
         <f t="shared" si="14"/>
         <v>78</v>
@@ -9656,8 +10934,11 @@
       <c r="D582" s="6" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="583" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E582" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="583" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A583">
         <f t="shared" si="14"/>
         <v>78</v>
@@ -9671,8 +10952,11 @@
       <c r="D583" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="584" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E583" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="584" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A584">
         <f t="shared" si="14"/>
         <v>78</v>
@@ -9686,8 +10970,11 @@
       <c r="D584" s="6" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="585" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E584" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="585" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A585">
         <f t="shared" si="14"/>
         <v>78</v>
@@ -9701,8 +10988,11 @@
       <c r="D585" s="6" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="586" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E585" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="586" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A586">
         <f t="shared" si="14"/>
         <v>78</v>
@@ -9716,8 +11006,11 @@
       <c r="D586" s="6" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="587" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E586" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="587" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A587">
         <f t="shared" si="14"/>
         <v>78</v>
@@ -9731,8 +11024,11 @@
       <c r="D587" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="588" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E587" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="588" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A588">
         <f t="shared" si="14"/>
         <v>78</v>
@@ -9746,8 +11042,11 @@
       <c r="D588" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="589" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E588" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="589" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A589">
         <f t="shared" si="14"/>
         <v>78</v>
@@ -9761,8 +11060,11 @@
       <c r="D589" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="590" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E589" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="590" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A590">
         <f t="shared" si="14"/>
         <v>78</v>
@@ -9776,8 +11078,11 @@
       <c r="D590" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="591" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E590" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="591" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A591">
         <f t="shared" si="14"/>
         <v>78</v>
@@ -9791,8 +11096,11 @@
       <c r="D591" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="592" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E591" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="592" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A592">
         <f t="shared" si="14"/>
         <v>78</v>
@@ -9806,8 +11114,11 @@
       <c r="D592" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="593" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E592" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="593" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A593">
         <f t="shared" si="14"/>
         <v>79</v>
@@ -9820,7 +11131,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="594" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A594">
         <f t="shared" si="14"/>
         <v>79</v>
@@ -9835,7 +11146,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="595" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A595">
         <f t="shared" si="14"/>
         <v>79</v>
@@ -9849,8 +11160,11 @@
       <c r="D595" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="596" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E595" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="596" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A596">
         <f t="shared" si="14"/>
         <v>79</v>
@@ -9864,8 +11178,11 @@
       <c r="D596" s="6" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="597" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E596" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="597" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A597">
         <f t="shared" si="14"/>
         <v>79</v>
@@ -9879,8 +11196,11 @@
       <c r="D597" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="598" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E597" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="598" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A598">
         <f t="shared" ref="A598:A652" si="15">IF(C599="Rendimiento",A597+1,A597)</f>
         <v>79</v>
@@ -9894,8 +11214,11 @@
       <c r="D598" s="6" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="599" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E598" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="599" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A599">
         <f t="shared" si="15"/>
         <v>79</v>
@@ -9909,8 +11232,11 @@
       <c r="D599" s="6" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="600" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E599" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="600" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A600">
         <f t="shared" si="15"/>
         <v>79</v>
@@ -9924,8 +11250,11 @@
       <c r="D600" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="601" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E600" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="601" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A601">
         <f t="shared" si="15"/>
         <v>79</v>
@@ -9939,8 +11268,11 @@
       <c r="D601" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="602" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E601" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="602" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A602">
         <f t="shared" si="15"/>
         <v>79</v>
@@ -9954,8 +11286,11 @@
       <c r="D602" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="603" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E602" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="603" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A603">
         <f t="shared" si="15"/>
         <v>79</v>
@@ -9969,8 +11304,11 @@
       <c r="D603" s="8" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="604" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E603" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="604" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A604">
         <f t="shared" si="15"/>
         <v>79</v>
@@ -9984,8 +11322,11 @@
       <c r="D604" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="605" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E604" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="605" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A605">
         <f t="shared" si="15"/>
         <v>80</v>
@@ -9998,7 +11339,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="606" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A606">
         <f t="shared" si="15"/>
         <v>80</v>
@@ -10013,7 +11354,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="607" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A607">
         <f t="shared" si="15"/>
         <v>80</v>
@@ -10027,8 +11368,11 @@
       <c r="D607" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="608" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E607" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="608" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A608">
         <f t="shared" si="15"/>
         <v>80</v>
@@ -10042,8 +11386,11 @@
       <c r="D608" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="609" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E608" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="609" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A609">
         <f t="shared" si="15"/>
         <v>80</v>
@@ -10057,8 +11404,11 @@
       <c r="D609" s="6" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="610" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E609" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="610" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A610">
         <f t="shared" si="15"/>
         <v>80</v>
@@ -10072,8 +11422,11 @@
       <c r="D610" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="611" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E610" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="611" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A611">
         <f t="shared" si="15"/>
         <v>80</v>
@@ -10087,8 +11440,11 @@
       <c r="D611" s="6" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="612" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E611" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="612" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A612">
         <f t="shared" si="15"/>
         <v>80</v>
@@ -10102,8 +11458,11 @@
       <c r="D612" s="6" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="613" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E612" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="613" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A613">
         <f t="shared" si="15"/>
         <v>80</v>
@@ -10117,8 +11476,11 @@
       <c r="D613" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="614" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E613" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="614" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A614">
         <f t="shared" si="15"/>
         <v>80</v>
@@ -10132,8 +11494,11 @@
       <c r="D614" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="615" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E614" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="615" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A615">
         <f t="shared" si="15"/>
         <v>80</v>
@@ -10147,8 +11512,11 @@
       <c r="D615" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="616" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E615" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="616" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A616">
         <f t="shared" si="15"/>
         <v>80</v>
@@ -10162,8 +11530,11 @@
       <c r="D616" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="617" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E616" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="617" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A617">
         <f t="shared" si="15"/>
         <v>80</v>
@@ -10177,8 +11548,11 @@
       <c r="D617" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="618" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E617" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="618" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A618">
         <f t="shared" si="15"/>
         <v>81</v>
@@ -10191,7 +11565,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="619" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A619">
         <f t="shared" si="15"/>
         <v>81</v>
@@ -10206,7 +11580,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="620" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A620">
         <f t="shared" si="15"/>
         <v>81</v>
@@ -10220,8 +11594,11 @@
       <c r="D620" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="621" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E620" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="621" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A621">
         <f t="shared" si="15"/>
         <v>81</v>
@@ -10235,8 +11612,11 @@
       <c r="D621" s="6" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="622" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E621" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="622" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A622">
         <f t="shared" si="15"/>
         <v>81</v>
@@ -10250,8 +11630,11 @@
       <c r="D622" s="6" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="623" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E622" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="623" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A623">
         <f t="shared" si="15"/>
         <v>81</v>
@@ -10265,8 +11648,11 @@
       <c r="D623" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="624" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E623" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="624" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A624">
         <f t="shared" si="15"/>
         <v>81</v>
@@ -10280,8 +11666,11 @@
       <c r="D624" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="625" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E624" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="625" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A625">
         <f t="shared" si="15"/>
         <v>82</v>
@@ -10294,7 +11683,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="626" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A626">
         <f t="shared" si="15"/>
         <v>82</v>
@@ -10309,7 +11698,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="627" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A627">
         <f t="shared" si="15"/>
         <v>82</v>
@@ -10323,8 +11712,11 @@
       <c r="D627" s="14" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="628" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E627" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="628" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A628">
         <f t="shared" si="15"/>
         <v>82</v>
@@ -10338,8 +11730,11 @@
       <c r="D628" s="14" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="629" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E628" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="629" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A629">
         <f t="shared" si="15"/>
         <v>82</v>
@@ -10353,8 +11748,11 @@
       <c r="D629" s="14" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="630" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E629" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="630" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A630">
         <f t="shared" si="15"/>
         <v>82</v>
@@ -10368,8 +11766,11 @@
       <c r="D630" s="14" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="631" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E630" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="631" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A631">
         <f t="shared" si="15"/>
         <v>82</v>
@@ -10383,8 +11784,11 @@
       <c r="D631" s="14" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="632" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E631" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="632" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A632">
         <f t="shared" si="15"/>
         <v>82</v>
@@ -10398,8 +11802,11 @@
       <c r="D632" s="16" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="633" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E632" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="633" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A633">
         <f t="shared" si="15"/>
         <v>83</v>
@@ -10412,7 +11819,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="634" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A634">
         <f t="shared" si="15"/>
         <v>83</v>
@@ -10427,7 +11834,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="635" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A635">
         <f t="shared" si="15"/>
         <v>83</v>
@@ -10441,8 +11848,11 @@
       <c r="D635" s="14" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="636" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E635" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="636" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A636">
         <f t="shared" si="15"/>
         <v>83</v>
@@ -10456,8 +11866,11 @@
       <c r="D636" s="14" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="637" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E636" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="637" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A637">
         <f t="shared" si="15"/>
         <v>83</v>
@@ -10471,8 +11884,11 @@
       <c r="D637" s="14" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="638" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E637" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="638" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A638">
         <f t="shared" si="15"/>
         <v>83</v>
@@ -10486,8 +11902,11 @@
       <c r="D638" s="14" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="639" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E638" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="639" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A639">
         <f t="shared" si="15"/>
         <v>83</v>
@@ -10501,8 +11920,11 @@
       <c r="D639" s="14" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="640" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E639" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="640" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A640">
         <f t="shared" si="15"/>
         <v>83</v>
@@ -10516,8 +11938,11 @@
       <c r="D640" s="16" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="641" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E640" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="641" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A641">
         <f t="shared" si="15"/>
         <v>84</v>
@@ -10530,7 +11955,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="642" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A642">
         <f t="shared" si="15"/>
         <v>84</v>
@@ -10545,7 +11970,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="643" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A643">
         <f t="shared" si="15"/>
         <v>84</v>
@@ -10559,8 +11984,11 @@
       <c r="D643" s="14" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="644" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E643" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="644" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A644">
         <f t="shared" si="15"/>
         <v>84</v>
@@ -10574,8 +12002,11 @@
       <c r="D644" s="14" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="645" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E644" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="645" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A645">
         <f t="shared" si="15"/>
         <v>84</v>
@@ -10589,8 +12020,11 @@
       <c r="D645" s="14" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="646" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E645" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="646" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A646">
         <f t="shared" si="15"/>
         <v>84</v>
@@ -10604,8 +12038,11 @@
       <c r="D646" s="14" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="647" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E646" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="647" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A647">
         <f t="shared" si="15"/>
         <v>84</v>
@@ -10619,8 +12056,11 @@
       <c r="D647" s="14" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="648" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E647" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="648" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A648">
         <f t="shared" si="15"/>
         <v>85</v>
@@ -10633,7 +12073,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="649" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A649">
         <f t="shared" si="15"/>
         <v>85</v>
@@ -10648,7 +12088,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="650" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A650">
         <f t="shared" si="15"/>
         <v>85</v>
@@ -10662,8 +12102,11 @@
       <c r="D650" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="651" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E650" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="651" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A651">
         <f t="shared" si="15"/>
         <v>85</v>
@@ -10677,8 +12120,11 @@
       <c r="D651" s="6" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="652" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E651" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="652" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A652">
         <f t="shared" si="15"/>
         <v>85</v>
@@ -10692,8 +12138,11 @@
       <c r="D652" s="6" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="653" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E652" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="653" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A653">
         <f t="shared" ref="A653:A692" si="16">IF(C654="Rendimiento",A652+1,A652)</f>
         <v>85</v>
@@ -10707,8 +12156,11 @@
       <c r="D653" s="6" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="654" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E653" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="654" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A654">
         <f t="shared" si="16"/>
         <v>85</v>
@@ -10722,8 +12174,11 @@
       <c r="D654" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="655" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E654" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="655" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A655">
         <f t="shared" si="16"/>
         <v>85</v>
@@ -10737,8 +12192,11 @@
       <c r="D655" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="656" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E655" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="656" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A656">
         <f t="shared" si="16"/>
         <v>86</v>
@@ -10751,7 +12209,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="657" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A657">
         <f t="shared" si="16"/>
         <v>86</v>
@@ -10766,7 +12224,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="658" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A658">
         <f t="shared" si="16"/>
         <v>86</v>
@@ -10780,8 +12238,11 @@
       <c r="D658" s="14" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="659" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E658" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="659" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A659">
         <f t="shared" si="16"/>
         <v>86</v>
@@ -10795,8 +12256,11 @@
       <c r="D659" s="14" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="660" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E659" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="660" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A660">
         <f t="shared" si="16"/>
         <v>86</v>
@@ -10810,8 +12274,11 @@
       <c r="D660" s="14" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="661" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E660" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="661" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A661">
         <f t="shared" si="16"/>
         <v>86</v>
@@ -10825,8 +12292,11 @@
       <c r="D661" s="14" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="662" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E661" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="662" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A662">
         <f t="shared" si="16"/>
         <v>86</v>
@@ -10840,8 +12310,11 @@
       <c r="D662" s="14" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="663" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E662" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="663" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A663">
         <f t="shared" si="16"/>
         <v>87</v>
@@ -10854,7 +12327,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="664" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A664">
         <f t="shared" si="16"/>
         <v>87</v>
@@ -10869,7 +12342,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="665" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A665">
         <f t="shared" si="16"/>
         <v>87</v>
@@ -10883,8 +12356,11 @@
       <c r="D665" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="666" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E665" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="666" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A666">
         <f t="shared" si="16"/>
         <v>87</v>
@@ -10898,8 +12374,11 @@
       <c r="D666" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="667" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E666" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="667" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A667">
         <f t="shared" si="16"/>
         <v>87</v>
@@ -10913,8 +12392,11 @@
       <c r="D667" s="8" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="668" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E667" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="668" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A668">
         <f t="shared" si="16"/>
         <v>87</v>
@@ -10928,8 +12410,11 @@
       <c r="D668" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="669" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E668" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="669" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A669">
         <f t="shared" si="16"/>
         <v>87</v>
@@ -10943,8 +12428,11 @@
       <c r="D669" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="670" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E669" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="670" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A670">
         <f t="shared" si="16"/>
         <v>88</v>
@@ -10957,7 +12445,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="671" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A671">
         <f t="shared" si="16"/>
         <v>88</v>
@@ -10972,7 +12460,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="672" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A672">
         <f t="shared" si="16"/>
         <v>88</v>
@@ -10986,8 +12474,11 @@
       <c r="D672" s="6" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="673" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E672" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="673" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A673">
         <f t="shared" si="16"/>
         <v>89</v>
@@ -11000,7 +12491,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="674" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A674">
         <f t="shared" si="16"/>
         <v>89</v>
@@ -11015,7 +12506,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="675" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A675">
         <f t="shared" si="16"/>
         <v>89</v>
@@ -11029,8 +12520,11 @@
       <c r="D675" s="14" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="676" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E675" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="676" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A676">
         <f t="shared" si="16"/>
         <v>89</v>
@@ -11044,8 +12538,11 @@
       <c r="D676" s="14" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="677" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E676" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="677" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A677">
         <f t="shared" si="16"/>
         <v>89</v>
@@ -11059,8 +12556,11 @@
       <c r="D677" s="14" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="678" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E677" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="678" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A678">
         <f t="shared" si="16"/>
         <v>90</v>
@@ -11073,7 +12573,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="679" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A679">
         <f t="shared" si="16"/>
         <v>90</v>
@@ -11088,7 +12588,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="680" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A680">
         <f t="shared" si="16"/>
         <v>90</v>
@@ -11102,8 +12602,11 @@
       <c r="D680" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="681" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E680" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="681" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A681">
         <f t="shared" si="16"/>
         <v>90</v>
@@ -11117,8 +12620,11 @@
       <c r="D681" s="6" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="682" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E681" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="682" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A682">
         <f t="shared" si="16"/>
         <v>90</v>
@@ -11132,8 +12638,11 @@
       <c r="D682" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="683" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E682" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="683" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A683">
         <f t="shared" si="16"/>
         <v>90</v>
@@ -11147,8 +12656,11 @@
       <c r="D683" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="684" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E683" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="684" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A684">
         <f t="shared" si="16"/>
         <v>90</v>
@@ -11162,8 +12674,11 @@
       <c r="D684" s="6" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="685" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E684" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="685" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A685">
         <f t="shared" si="16"/>
         <v>90</v>
@@ -11177,8 +12692,11 @@
       <c r="D685" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="686" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E685" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="686" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A686">
         <f t="shared" si="16"/>
         <v>90</v>
@@ -11192,8 +12710,11 @@
       <c r="D686" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="687" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E686" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="687" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A687">
         <f t="shared" si="16"/>
         <v>91</v>
@@ -11206,7 +12727,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="688" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A688">
         <f t="shared" si="16"/>
         <v>91</v>
@@ -11221,109 +12742,130 @@
         <v>5</v>
       </c>
     </row>
-    <row r="689" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A689">
         <f t="shared" si="16"/>
         <v>91</v>
       </c>
-      <c r="B689" s="24" t="s">
+      <c r="B689" s="23" t="s">
         <v>56</v>
       </c>
-      <c r="C689" s="25">
+      <c r="C689" s="24">
         <v>17</v>
       </c>
-      <c r="D689" s="25" t="s">
+      <c r="D689" s="24" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="690" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E689" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="690" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A690">
         <f t="shared" si="16"/>
         <v>91</v>
       </c>
-      <c r="B690" s="24" t="s">
+      <c r="B690" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="C690" s="25">
+      <c r="C690" s="24">
         <v>1.05</v>
       </c>
-      <c r="D690" s="25" t="s">
+      <c r="D690" s="24" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="691" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E690" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="691" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A691">
         <f t="shared" si="16"/>
         <v>91</v>
       </c>
-      <c r="B691" s="24" t="s">
+      <c r="B691" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="C691" s="25">
+      <c r="C691" s="24">
         <v>0.1</v>
       </c>
-      <c r="D691" s="25" t="s">
+      <c r="D691" s="24" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="692" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E691" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="692" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A692">
         <f t="shared" si="16"/>
         <v>91</v>
       </c>
-      <c r="B692" s="24" t="s">
+      <c r="B692" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="C692" s="25">
+      <c r="C692" s="24">
         <v>0.3</v>
       </c>
-      <c r="D692" s="25" t="s">
+      <c r="D692" s="24" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="693" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E692" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="693" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A693">
         <f t="shared" ref="A693:A695" si="17">IF(C694="Rendimiento",A692+1,A692)</f>
         <v>91</v>
       </c>
-      <c r="B693" s="24" t="s">
+      <c r="B693" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="C693" s="25">
+      <c r="C693" s="24">
         <v>9</v>
       </c>
-      <c r="D693" s="25" t="s">
+      <c r="D693" s="24" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="694" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E693" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="694" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A694">
         <f t="shared" si="17"/>
         <v>91</v>
       </c>
-      <c r="B694" s="24" t="s">
+      <c r="B694" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="C694" s="25">
+      <c r="C694" s="24">
         <v>2</v>
       </c>
-      <c r="D694" s="25" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="695" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D694" s="24" t="s">
+        <v>189</v>
+      </c>
+      <c r="E694" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="695" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A695">
         <f t="shared" si="17"/>
         <v>91</v>
       </c>
-      <c r="B695" s="24" t="s">
+      <c r="B695" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="C695" s="25">
+      <c r="C695" s="24">
         <v>2.5</v>
       </c>
-      <c r="D695" s="25" t="s">
-        <v>189</v>
+      <c r="D695" s="24" t="s">
+        <v>189</v>
+      </c>
+      <c r="E695" t="s">
+        <v>194</v>
       </c>
     </row>
   </sheetData>
@@ -11345,12 +12887,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6765BC3E-412B-49F6-B49E-D97CF62A3ED1}">
   <dimension ref="A1:B91"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="43.28515625" customWidth="1"/>
+    <col min="2" max="2" width="43.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1">
         <v>1</v>
       </c>
@@ -11358,7 +12900,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>2</v>
       </c>
@@ -11366,7 +12908,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>3</v>
       </c>
@@ -11374,7 +12916,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>4</v>
       </c>
@@ -11382,7 +12924,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>5</v>
       </c>
@@ -11390,7 +12932,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>6</v>
       </c>
@@ -11398,7 +12940,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>7</v>
       </c>
@@ -11406,7 +12948,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>8</v>
       </c>
@@ -11414,7 +12956,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>9</v>
       </c>
@@ -11422,7 +12964,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>10</v>
       </c>
@@ -11430,7 +12972,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>11</v>
       </c>
@@ -11438,7 +12980,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>12</v>
       </c>
@@ -11446,7 +12988,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>13</v>
       </c>
@@ -11454,7 +12996,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>14</v>
       </c>
@@ -11462,7 +13004,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>15</v>
       </c>
@@ -11470,7 +13012,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>16</v>
       </c>
@@ -11478,7 +13020,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>17</v>
       </c>
@@ -11486,7 +13028,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>18</v>
       </c>
@@ -11494,7 +13036,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>19</v>
       </c>
@@ -11502,7 +13044,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>20</v>
       </c>
@@ -11510,7 +13052,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>21</v>
       </c>
@@ -11518,7 +13060,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>22</v>
       </c>
@@ -11526,7 +13068,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>23</v>
       </c>
@@ -11534,7 +13076,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>24</v>
       </c>
@@ -11542,7 +13084,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>25</v>
       </c>
@@ -11550,7 +13092,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>26</v>
       </c>
@@ -11558,7 +13100,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>27</v>
       </c>
@@ -11566,7 +13108,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>28</v>
       </c>
@@ -11574,7 +13116,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>29</v>
       </c>
@@ -11582,7 +13124,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>30</v>
       </c>
@@ -11590,7 +13132,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>31</v>
       </c>
@@ -11598,7 +13140,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>32</v>
       </c>
@@ -11606,7 +13148,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>33</v>
       </c>
@@ -11614,7 +13156,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>34</v>
       </c>
@@ -11622,7 +13164,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>35</v>
       </c>
@@ -11630,7 +13172,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>36</v>
       </c>
@@ -11638,7 +13180,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>37</v>
       </c>
@@ -11646,7 +13188,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>38</v>
       </c>
@@ -11654,7 +13196,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>39</v>
       </c>
@@ -11662,7 +13204,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>40</v>
       </c>
@@ -11670,7 +13212,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>41</v>
       </c>
@@ -11678,7 +13220,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>42</v>
       </c>
@@ -11686,7 +13228,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>43</v>
       </c>
@@ -11694,7 +13236,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>44</v>
       </c>
@@ -11702,7 +13244,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>45</v>
       </c>
@@ -11710,7 +13252,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>46</v>
       </c>
@@ -11718,7 +13260,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>47</v>
       </c>
@@ -11726,7 +13268,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>48</v>
       </c>
@@ -11734,7 +13276,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>49</v>
       </c>
@@ -11742,7 +13284,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>50</v>
       </c>
@@ -11750,7 +13292,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>51</v>
       </c>
@@ -11758,7 +13300,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>52</v>
       </c>
@@ -11766,7 +13308,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>53</v>
       </c>
@@ -11774,7 +13316,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>54</v>
       </c>
@@ -11782,7 +13324,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>55</v>
       </c>
@@ -11790,7 +13332,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>56</v>
       </c>
@@ -11798,7 +13340,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>57</v>
       </c>
@@ -11806,7 +13348,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>58</v>
       </c>
@@ -11814,7 +13356,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>59</v>
       </c>
@@ -11822,7 +13364,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>60</v>
       </c>
@@ -11830,7 +13372,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>61</v>
       </c>
@@ -11838,7 +13380,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>62</v>
       </c>
@@ -11846,7 +13388,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>63</v>
       </c>
@@ -11854,7 +13396,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>64</v>
       </c>
@@ -11862,7 +13404,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>65</v>
       </c>
@@ -11870,7 +13412,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>66</v>
       </c>
@@ -11878,7 +13420,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>67</v>
       </c>
@@ -11886,7 +13428,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>68</v>
       </c>
@@ -11894,7 +13436,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>69</v>
       </c>
@@ -11902,7 +13444,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>70</v>
       </c>
@@ -11910,7 +13452,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>71</v>
       </c>
@@ -11918,7 +13460,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>72</v>
       </c>
@@ -11926,7 +13468,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>73</v>
       </c>
@@ -11934,7 +13476,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>74</v>
       </c>
@@ -11942,7 +13484,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>75</v>
       </c>
@@ -11950,7 +13492,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>76</v>
       </c>
@@ -11958,7 +13500,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>77</v>
       </c>
@@ -11966,7 +13508,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>78</v>
       </c>
@@ -11974,7 +13516,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>79</v>
       </c>
@@ -11982,7 +13524,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>80</v>
       </c>
@@ -11990,7 +13532,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>81</v>
       </c>
@@ -11998,7 +13540,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>82</v>
       </c>
@@ -12006,7 +13548,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>83</v>
       </c>
@@ -12014,7 +13556,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>84</v>
       </c>
@@ -12022,7 +13564,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>85</v>
       </c>
@@ -12030,7 +13572,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>86</v>
       </c>
@@ -12038,7 +13580,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>87</v>
       </c>
@@ -12046,7 +13588,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>88</v>
       </c>
@@ -12054,7 +13596,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>89</v>
       </c>
@@ -12062,7 +13604,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>90</v>
       </c>
@@ -12070,7 +13612,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>91</v>
       </c>
